--- a/artfynd/A 28856-2025 artfynd.xlsx
+++ b/artfynd/A 28856-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131046803</v>
+        <v>131046875</v>
       </c>
       <c r="B2" t="n">
-        <v>79002</v>
+        <v>79246</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>395450</v>
+        <v>395444</v>
       </c>
       <c r="R2" t="n">
-        <v>6804390</v>
+        <v>6804461</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131046875</v>
+        <v>131046803</v>
       </c>
       <c r="B3" t="n">
-        <v>79245</v>
+        <v>79003</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>395444</v>
+        <v>395450</v>
       </c>
       <c r="R3" t="n">
-        <v>6804461</v>
+        <v>6804390</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131046947</v>
+        <v>131046995</v>
       </c>
       <c r="B4" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>395461</v>
+        <v>395491</v>
       </c>
       <c r="R4" t="n">
-        <v>6804551</v>
+        <v>6804522</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131046872</v>
+        <v>131046747</v>
       </c>
       <c r="B5" t="n">
-        <v>79245</v>
+        <v>57881</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,34 +1007,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>395434</v>
+        <v>395480</v>
       </c>
       <c r="R5" t="n">
-        <v>6804484</v>
+        <v>6804496</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1081,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131046873</v>
+        <v>131046947</v>
       </c>
       <c r="B6" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1138,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>395430</v>
+        <v>395461</v>
       </c>
       <c r="R6" t="n">
-        <v>6804474</v>
+        <v>6804551</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131046995</v>
+        <v>131046896</v>
       </c>
       <c r="B7" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1245,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>395491</v>
+        <v>395423</v>
       </c>
       <c r="R7" t="n">
-        <v>6804522</v>
+        <v>6804458</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1285,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1295,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,10 +1322,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131046896</v>
+        <v>131046872</v>
       </c>
       <c r="B8" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1352,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>395423</v>
+        <v>395434</v>
       </c>
       <c r="R8" t="n">
-        <v>6804458</v>
+        <v>6804484</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,7 +1392,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1402,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,10 +1429,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131046747</v>
+        <v>131046873</v>
       </c>
       <c r="B9" t="n">
-        <v>57881</v>
+        <v>79246</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1435,39 +1440,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>395480</v>
+        <v>395430</v>
       </c>
       <c r="R9" t="n">
-        <v>6804496</v>
+        <v>6804474</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1653,10 +1653,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131046749</v>
+        <v>131033342</v>
       </c>
       <c r="B11" t="n">
-        <v>57881</v>
+        <v>79246</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1664,39 +1664,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>395449</v>
+        <v>395753</v>
       </c>
       <c r="R11" t="n">
-        <v>6804395</v>
+        <v>6804557</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1723,22 +1718,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1765,10 +1760,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131033342</v>
+        <v>131046858</v>
       </c>
       <c r="B12" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1800,10 +1795,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>395753</v>
+        <v>395570</v>
       </c>
       <c r="R12" t="n">
-        <v>6804557</v>
+        <v>6804341</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1830,22 +1825,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1872,10 +1867,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131046884</v>
+        <v>131046749</v>
       </c>
       <c r="B13" t="n">
-        <v>79245</v>
+        <v>57881</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1883,34 +1878,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>395489</v>
+        <v>395449</v>
       </c>
       <c r="R13" t="n">
-        <v>6804292</v>
+        <v>6804395</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1979,10 +1979,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131046858</v>
+        <v>131046884</v>
       </c>
       <c r="B14" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2014,10 +2014,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>395570</v>
+        <v>395489</v>
       </c>
       <c r="R14" t="n">
-        <v>6804341</v>
+        <v>6804292</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2049,7 +2049,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2089,7 +2089,7 @@
         <v>131046807</v>
       </c>
       <c r="B15" t="n">
-        <v>83208</v>
+        <v>83209</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2193,10 +2193,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131047009</v>
+        <v>131046868</v>
       </c>
       <c r="B16" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2204,42 +2204,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>395494</v>
+        <v>395462</v>
       </c>
       <c r="R16" t="n">
-        <v>6804551</v>
+        <v>6804496</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2271,7 +2263,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2281,12 +2273,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:26</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Nästan helt avbarkad klen gran</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2313,10 +2300,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131033283</v>
+        <v>131046901</v>
       </c>
       <c r="B17" t="n">
-        <v>79277</v>
+        <v>79246</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2324,21 +2311,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2348,10 +2335,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>395745</v>
+        <v>395395</v>
       </c>
       <c r="R17" t="n">
-        <v>6804404</v>
+        <v>6804547</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2378,22 +2365,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2420,10 +2407,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131033331</v>
+        <v>131033348</v>
       </c>
       <c r="B18" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2455,10 +2442,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>395707</v>
+        <v>395756</v>
       </c>
       <c r="R18" t="n">
-        <v>6804307</v>
+        <v>6804343</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2490,7 +2477,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2500,7 +2487,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2527,10 +2514,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131046901</v>
+        <v>131046955</v>
       </c>
       <c r="B19" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2562,10 +2549,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>395395</v>
+        <v>395432</v>
       </c>
       <c r="R19" t="n">
-        <v>6804547</v>
+        <v>6804533</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2597,7 +2584,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2607,7 +2594,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2634,10 +2621,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131046955</v>
+        <v>131046878</v>
       </c>
       <c r="B20" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2669,10 +2656,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>395432</v>
+        <v>395478</v>
       </c>
       <c r="R20" t="n">
-        <v>6804533</v>
+        <v>6804426</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2704,7 +2691,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2714,7 +2701,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2741,10 +2728,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131046878</v>
+        <v>131046777</v>
       </c>
       <c r="B21" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2752,34 +2739,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>395478</v>
+        <v>395435</v>
       </c>
       <c r="R21" t="n">
-        <v>6804426</v>
+        <v>6804481</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2811,7 +2803,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2821,7 +2813,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2848,10 +2845,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131046868</v>
+        <v>131047009</v>
       </c>
       <c r="B22" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2859,34 +2856,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>395462</v>
+        <v>395494</v>
       </c>
       <c r="R22" t="n">
-        <v>6804496</v>
+        <v>6804551</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2918,7 +2923,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2928,7 +2933,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Nästan helt avbarkad klen gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2955,10 +2965,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131033348</v>
+        <v>131033283</v>
       </c>
       <c r="B23" t="n">
-        <v>79245</v>
+        <v>79278</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2966,21 +2976,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2990,10 +3000,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>395756</v>
+        <v>395745</v>
       </c>
       <c r="R23" t="n">
-        <v>6804343</v>
+        <v>6804404</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3025,7 +3035,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3035,7 +3045,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3062,10 +3072,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131046777</v>
+        <v>131033331</v>
       </c>
       <c r="B24" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3073,39 +3083,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>395435</v>
+        <v>395707</v>
       </c>
       <c r="R24" t="n">
-        <v>6804481</v>
+        <v>6804307</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3132,27 +3137,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:46</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3179,10 +3179,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131033294</v>
+        <v>131033324</v>
       </c>
       <c r="B25" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3190,39 +3190,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>395714</v>
+        <v>395676</v>
       </c>
       <c r="R25" t="n">
-        <v>6804552</v>
+        <v>6804490</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3254,7 +3249,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3264,12 +3259,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:06</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3296,10 +3286,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131033324</v>
+        <v>131033294</v>
       </c>
       <c r="B26" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3307,34 +3297,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>395676</v>
+        <v>395714</v>
       </c>
       <c r="R26" t="n">
-        <v>6804490</v>
+        <v>6804552</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3366,7 +3361,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3376,7 +3371,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3403,10 +3403,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131046894</v>
+        <v>131033344</v>
       </c>
       <c r="B27" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3438,10 +3438,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>395429</v>
+        <v>395753</v>
       </c>
       <c r="R27" t="n">
-        <v>6804421</v>
+        <v>6804482</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3468,22 +3468,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3510,10 +3510,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131033344</v>
+        <v>131046894</v>
       </c>
       <c r="B28" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3545,10 +3545,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>395753</v>
+        <v>395429</v>
       </c>
       <c r="R28" t="n">
-        <v>6804482</v>
+        <v>6804421</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3575,22 +3575,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3620,7 +3620,7 @@
         <v>131033302</v>
       </c>
       <c r="B29" t="n">
-        <v>79003</v>
+        <v>79004</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3724,45 +3724,50 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131046885</v>
+        <v>131047035</v>
       </c>
       <c r="B30" t="n">
-        <v>79245</v>
+        <v>5177</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>395486</v>
+        <v>395505</v>
       </c>
       <c r="R30" t="n">
-        <v>6804289</v>
+        <v>6804295</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3794,7 +3799,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3804,7 +3809,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3831,10 +3836,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131046892</v>
+        <v>131046994</v>
       </c>
       <c r="B31" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3866,10 +3871,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>395445</v>
+        <v>395484</v>
       </c>
       <c r="R31" t="n">
-        <v>6804404</v>
+        <v>6804534</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3901,7 +3906,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3911,7 +3916,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3938,10 +3943,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131046898</v>
+        <v>131046885</v>
       </c>
       <c r="B32" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3973,10 +3978,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>395393</v>
+        <v>395486</v>
       </c>
       <c r="R32" t="n">
-        <v>6804503</v>
+        <v>6804289</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4008,7 +4013,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4018,7 +4023,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4045,10 +4050,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131046994</v>
+        <v>131046956</v>
       </c>
       <c r="B33" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4080,10 +4085,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>395484</v>
+        <v>395418</v>
       </c>
       <c r="R33" t="n">
-        <v>6804534</v>
+        <v>6804552</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4115,7 +4120,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4125,7 +4130,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4152,10 +4157,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131046956</v>
+        <v>131046892</v>
       </c>
       <c r="B34" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4187,10 +4192,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>395418</v>
+        <v>395445</v>
       </c>
       <c r="R34" t="n">
-        <v>6804552</v>
+        <v>6804404</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4222,7 +4227,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4232,7 +4237,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4259,10 +4264,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131046998</v>
+        <v>131046898</v>
       </c>
       <c r="B35" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4294,10 +4299,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>395494</v>
+        <v>395393</v>
       </c>
       <c r="R35" t="n">
-        <v>6804551</v>
+        <v>6804503</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4329,7 +4334,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4339,7 +4344,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4366,50 +4371,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131047035</v>
+        <v>131046998</v>
       </c>
       <c r="B36" t="n">
-        <v>5177</v>
+        <v>79246</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>395505</v>
+        <v>395494</v>
       </c>
       <c r="R36" t="n">
-        <v>6804295</v>
+        <v>6804551</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4481,7 +4481,7 @@
         <v>131046855</v>
       </c>
       <c r="B37" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4588,7 +4588,7 @@
         <v>131046897</v>
       </c>
       <c r="B38" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4695,7 +4695,7 @@
         <v>131033347</v>
       </c>
       <c r="B39" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4799,10 +4799,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131046805</v>
+        <v>131033288</v>
       </c>
       <c r="B40" t="n">
-        <v>79002</v>
+        <v>57884</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4810,34 +4810,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>395461</v>
+        <v>395651</v>
       </c>
       <c r="R40" t="n">
-        <v>6804539</v>
+        <v>6804457</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4864,22 +4869,27 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4906,10 +4916,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131033334</v>
+        <v>131046748</v>
       </c>
       <c r="B41" t="n">
-        <v>79245</v>
+        <v>57881</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4917,34 +4927,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>395718</v>
+        <v>395453</v>
       </c>
       <c r="R41" t="n">
-        <v>6804558</v>
+        <v>6804322</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4971,22 +4986,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5016,7 +5031,7 @@
         <v>131046881</v>
       </c>
       <c r="B42" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5120,10 +5135,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131046999</v>
+        <v>131033334</v>
       </c>
       <c r="B43" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5155,10 +5170,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>395485</v>
+        <v>395718</v>
       </c>
       <c r="R43" t="n">
-        <v>6804561</v>
+        <v>6804558</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5185,22 +5200,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5227,10 +5242,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131033346</v>
+        <v>131046999</v>
       </c>
       <c r="B44" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5262,10 +5277,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>395744</v>
+        <v>395485</v>
       </c>
       <c r="R44" t="n">
-        <v>6804417</v>
+        <v>6804561</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5292,22 +5307,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5337,7 +5352,7 @@
         <v>131046859</v>
       </c>
       <c r="B45" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5441,10 +5456,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131046748</v>
+        <v>131046805</v>
       </c>
       <c r="B46" t="n">
-        <v>57881</v>
+        <v>79003</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5452,39 +5467,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>395453</v>
+        <v>395461</v>
       </c>
       <c r="R46" t="n">
-        <v>6804322</v>
+        <v>6804539</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5516,7 +5526,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5526,7 +5536,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5553,10 +5563,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131033288</v>
+        <v>131033346</v>
       </c>
       <c r="B47" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5564,39 +5574,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>395651</v>
+        <v>395744</v>
       </c>
       <c r="R47" t="n">
-        <v>6804457</v>
+        <v>6804417</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5628,7 +5633,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5638,12 +5643,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:42</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5670,10 +5670,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131033323</v>
+        <v>131046866</v>
       </c>
       <c r="B48" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5705,10 +5705,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>395680</v>
+        <v>395542</v>
       </c>
       <c r="R48" t="n">
-        <v>6804541</v>
+        <v>6804432</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5735,22 +5735,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5777,10 +5777,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131046949</v>
+        <v>131046954</v>
       </c>
       <c r="B49" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5812,10 +5812,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>395463</v>
+        <v>395446</v>
       </c>
       <c r="R49" t="n">
-        <v>6804534</v>
+        <v>6804531</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5847,7 +5847,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5857,7 +5857,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5884,10 +5884,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131046866</v>
+        <v>131046997</v>
       </c>
       <c r="B50" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5919,10 +5919,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>395542</v>
+        <v>395518</v>
       </c>
       <c r="R50" t="n">
-        <v>6804432</v>
+        <v>6804527</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5954,7 +5954,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5964,7 +5964,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5991,10 +5991,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131046880</v>
+        <v>131046861</v>
       </c>
       <c r="B51" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6026,10 +6026,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>395491</v>
+        <v>395564</v>
       </c>
       <c r="R51" t="n">
-        <v>6804393</v>
+        <v>6804373</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6061,7 +6061,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6071,7 +6071,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6098,10 +6098,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131046869</v>
+        <v>131033323</v>
       </c>
       <c r="B52" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6133,10 +6133,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>395456</v>
+        <v>395680</v>
       </c>
       <c r="R52" t="n">
-        <v>6804500</v>
+        <v>6804541</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6163,22 +6163,22 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6205,10 +6205,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131046954</v>
+        <v>131033352</v>
       </c>
       <c r="B53" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6240,10 +6240,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>395446</v>
+        <v>395857</v>
       </c>
       <c r="R53" t="n">
-        <v>6804531</v>
+        <v>6804292</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6270,22 +6270,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6312,10 +6312,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131046997</v>
+        <v>131046949</v>
       </c>
       <c r="B54" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6347,10 +6347,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>395518</v>
+        <v>395463</v>
       </c>
       <c r="R54" t="n">
-        <v>6804527</v>
+        <v>6804534</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6382,7 +6382,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6392,7 +6392,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6419,10 +6419,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131046861</v>
+        <v>131046948</v>
       </c>
       <c r="B55" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6454,10 +6454,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>395564</v>
+        <v>395462</v>
       </c>
       <c r="R55" t="n">
-        <v>6804373</v>
+        <v>6804542</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6489,7 +6489,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6499,7 +6499,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6526,10 +6526,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131046712</v>
+        <v>131046880</v>
       </c>
       <c r="B56" t="n">
-        <v>83225</v>
+        <v>79246</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6537,21 +6537,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6561,10 +6561,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>395468</v>
+        <v>395491</v>
       </c>
       <c r="R56" t="n">
-        <v>6804494</v>
+        <v>6804393</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6596,7 +6596,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6606,7 +6606,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6633,10 +6633,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131033352</v>
+        <v>131046869</v>
       </c>
       <c r="B57" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6668,10 +6668,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>395857</v>
+        <v>395456</v>
       </c>
       <c r="R57" t="n">
-        <v>6804292</v>
+        <v>6804500</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6698,22 +6698,22 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6740,10 +6740,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131046948</v>
+        <v>131046712</v>
       </c>
       <c r="B58" t="n">
-        <v>79245</v>
+        <v>83226</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6751,21 +6751,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6775,10 +6775,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>395462</v>
+        <v>395468</v>
       </c>
       <c r="R58" t="n">
-        <v>6804542</v>
+        <v>6804494</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6810,7 +6810,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6820,7 +6820,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6847,10 +6847,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131046874</v>
+        <v>131046879</v>
       </c>
       <c r="B59" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6882,10 +6882,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>395433</v>
+        <v>395482</v>
       </c>
       <c r="R59" t="n">
-        <v>6804469</v>
+        <v>6804421</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6917,7 +6917,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6954,10 +6954,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131046888</v>
+        <v>131046874</v>
       </c>
       <c r="B60" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6989,10 +6989,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>395436</v>
+        <v>395433</v>
       </c>
       <c r="R60" t="n">
-        <v>6804373</v>
+        <v>6804469</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7024,7 +7024,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7061,10 +7061,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131046713</v>
+        <v>131046888</v>
       </c>
       <c r="B61" t="n">
-        <v>83225</v>
+        <v>79246</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7072,21 +7072,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7096,10 +7096,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>395454</v>
+        <v>395436</v>
       </c>
       <c r="R61" t="n">
-        <v>6804501</v>
+        <v>6804373</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7131,7 +7131,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7141,7 +7141,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7168,10 +7168,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131046879</v>
+        <v>131046713</v>
       </c>
       <c r="B62" t="n">
-        <v>79245</v>
+        <v>83226</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7179,21 +7179,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7203,10 +7203,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>395482</v>
+        <v>395454</v>
       </c>
       <c r="R62" t="n">
-        <v>6804421</v>
+        <v>6804501</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7238,7 +7238,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7248,7 +7248,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7275,10 +7275,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131033321</v>
+        <v>131046996</v>
       </c>
       <c r="B63" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7310,10 +7310,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>395718</v>
+        <v>395485</v>
       </c>
       <c r="R63" t="n">
-        <v>6804573</v>
+        <v>6804506</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7340,22 +7340,22 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7382,10 +7382,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131046882</v>
+        <v>131033321</v>
       </c>
       <c r="B64" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7417,10 +7417,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>395493</v>
+        <v>395718</v>
       </c>
       <c r="R64" t="n">
-        <v>6804376</v>
+        <v>6804573</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7447,22 +7447,22 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7489,10 +7489,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131046996</v>
+        <v>131046882</v>
       </c>
       <c r="B65" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7524,10 +7524,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>395485</v>
+        <v>395493</v>
       </c>
       <c r="R65" t="n">
-        <v>6804506</v>
+        <v>6804376</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7569,7 +7569,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7599,7 +7599,7 @@
         <v>131033327</v>
       </c>
       <c r="B66" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7706,7 +7706,7 @@
         <v>131033326</v>
       </c>
       <c r="B67" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7927,10 +7927,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131033353</v>
+        <v>131046993</v>
       </c>
       <c r="B69" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7962,10 +7962,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>395859</v>
+        <v>395472</v>
       </c>
       <c r="R69" t="n">
-        <v>6804312</v>
+        <v>6804550</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7992,22 +7992,22 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8034,32 +8034,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131033299</v>
+        <v>131033353</v>
       </c>
       <c r="B70" t="n">
-        <v>79269</v>
+        <v>79246</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8069,10 +8069,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>395890</v>
+        <v>395859</v>
       </c>
       <c r="R70" t="n">
-        <v>6804464</v>
+        <v>6804312</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8104,7 +8104,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8114,7 +8114,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8141,10 +8141,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131046993</v>
+        <v>131046856</v>
       </c>
       <c r="B71" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8176,10 +8176,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>395472</v>
+        <v>395564</v>
       </c>
       <c r="R71" t="n">
-        <v>6804550</v>
+        <v>6804311</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8211,7 +8211,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8221,7 +8221,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8248,10 +8248,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131046856</v>
+        <v>131046877</v>
       </c>
       <c r="B72" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8283,10 +8283,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>395564</v>
+        <v>395464</v>
       </c>
       <c r="R72" t="n">
-        <v>6804311</v>
+        <v>6804442</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8318,7 +8318,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8328,7 +8328,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8355,10 +8355,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131046877</v>
+        <v>131033295</v>
       </c>
       <c r="B73" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8366,34 +8366,39 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>395464</v>
+        <v>395744</v>
       </c>
       <c r="R73" t="n">
-        <v>6804442</v>
+        <v>6804575</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8420,22 +8425,27 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8462,50 +8472,45 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131033295</v>
+        <v>131033299</v>
       </c>
       <c r="B74" t="n">
-        <v>57884</v>
+        <v>79270</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>6434</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>395744</v>
+        <v>395890</v>
       </c>
       <c r="R74" t="n">
-        <v>6804575</v>
+        <v>6804464</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8537,7 +8542,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8547,12 +8552,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>13:09</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8582,7 +8582,7 @@
         <v>131046865</v>
       </c>
       <c r="B75" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8686,10 +8686,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131046886</v>
+        <v>131046862</v>
       </c>
       <c r="B76" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8721,10 +8721,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>395447</v>
+        <v>395554</v>
       </c>
       <c r="R76" t="n">
-        <v>6804315</v>
+        <v>6804375</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8756,7 +8756,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8766,7 +8766,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8793,10 +8793,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131046862</v>
+        <v>131046886</v>
       </c>
       <c r="B77" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8828,10 +8828,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>395554</v>
+        <v>395447</v>
       </c>
       <c r="R77" t="n">
-        <v>6804375</v>
+        <v>6804315</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8863,7 +8863,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8873,7 +8873,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8903,7 +8903,7 @@
         <v>131033303</v>
       </c>
       <c r="B78" t="n">
-        <v>79003</v>
+        <v>79004</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
         <v>131046854</v>
       </c>
       <c r="B79" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9117,7 +9117,7 @@
         <v>131033330</v>
       </c>
       <c r="B80" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9224,7 +9224,7 @@
         <v>131033322</v>
       </c>
       <c r="B81" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9331,7 +9331,7 @@
         <v>131046883</v>
       </c>
       <c r="B82" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9435,10 +9435,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>131046857</v>
+        <v>131046889</v>
       </c>
       <c r="B83" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9470,10 +9470,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>395560</v>
+        <v>395429</v>
       </c>
       <c r="R83" t="n">
-        <v>6804326</v>
+        <v>6804384</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9505,7 +9505,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9515,7 +9515,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9542,10 +9542,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>131046889</v>
+        <v>131046857</v>
       </c>
       <c r="B84" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9577,10 +9577,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>395429</v>
+        <v>395560</v>
       </c>
       <c r="R84" t="n">
-        <v>6804384</v>
+        <v>6804326</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9612,7 +9612,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9622,7 +9622,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9652,7 +9652,7 @@
         <v>131046893</v>
       </c>
       <c r="B85" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9756,10 +9756,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131047018</v>
+        <v>131033333</v>
       </c>
       <c r="B86" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9767,39 +9767,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>395509</v>
+        <v>395717</v>
       </c>
       <c r="R86" t="n">
-        <v>6804287</v>
+        <v>6804542</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9826,34 +9821,29 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>10:17</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Troliga spår efter tretåig hackspett (barkfälkning)</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
       <c r="AE86" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG86" t="b">
         <v>0</v>
@@ -9873,10 +9863,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>131033293</v>
+        <v>131046902</v>
       </c>
       <c r="B87" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9884,39 +9874,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>395668</v>
+        <v>395389</v>
       </c>
       <c r="R87" t="n">
-        <v>6804432</v>
+        <v>6804555</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9943,27 +9928,22 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>12:22</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9990,10 +9970,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>131033333</v>
+        <v>131046860</v>
       </c>
       <c r="B88" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10025,10 +10005,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>395717</v>
+        <v>395578</v>
       </c>
       <c r="R88" t="n">
-        <v>6804542</v>
+        <v>6804350</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10055,22 +10035,22 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10097,10 +10077,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>131046902</v>
+        <v>131047018</v>
       </c>
       <c r="B89" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10108,34 +10088,39 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>395389</v>
+        <v>395509</v>
       </c>
       <c r="R89" t="n">
-        <v>6804555</v>
+        <v>6804287</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10167,7 +10152,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10177,14 +10162,19 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Troliga spår efter tretåig hackspett (barkfälkning)</t>
         </is>
       </c>
       <c r="AD89" t="b">
         <v>0</v>
       </c>
       <c r="AE89" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG89" t="b">
         <v>0</v>
@@ -10204,10 +10194,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>131046860</v>
+        <v>131033293</v>
       </c>
       <c r="B90" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10215,34 +10205,39 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>395578</v>
+        <v>395668</v>
       </c>
       <c r="R90" t="n">
-        <v>6804350</v>
+        <v>6804432</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10269,22 +10264,27 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10311,10 +10311,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>131046950</v>
+        <v>131046891</v>
       </c>
       <c r="B91" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10346,10 +10346,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>395470</v>
+        <v>395453</v>
       </c>
       <c r="R91" t="n">
-        <v>6804530</v>
+        <v>6804400</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10391,7 +10391,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10418,10 +10418,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>131046870</v>
+        <v>131046950</v>
       </c>
       <c r="B92" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10453,10 +10453,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>395450</v>
+        <v>395470</v>
       </c>
       <c r="R92" t="n">
-        <v>6804507</v>
+        <v>6804530</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10488,7 +10488,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10498,7 +10498,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10525,10 +10525,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>131046891</v>
+        <v>131033345</v>
       </c>
       <c r="B93" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10560,10 +10560,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>395453</v>
+        <v>395748</v>
       </c>
       <c r="R93" t="n">
-        <v>6804400</v>
+        <v>6804429</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10590,22 +10590,22 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10632,10 +10632,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>131033345</v>
+        <v>131046870</v>
       </c>
       <c r="B94" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10667,10 +10667,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>395748</v>
+        <v>395450</v>
       </c>
       <c r="R94" t="n">
-        <v>6804429</v>
+        <v>6804507</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10697,22 +10697,22 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10742,7 +10742,7 @@
         <v>131046992</v>
       </c>
       <c r="B95" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10846,10 +10846,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>131046887</v>
+        <v>131033362</v>
       </c>
       <c r="B96" t="n">
-        <v>79245</v>
+        <v>78912</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10857,21 +10857,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10881,10 +10881,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>395449</v>
+        <v>395883</v>
       </c>
       <c r="R96" t="n">
-        <v>6804334</v>
+        <v>6804433</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10911,22 +10911,22 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10953,10 +10953,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>131033362</v>
+        <v>131033332</v>
       </c>
       <c r="B97" t="n">
-        <v>78911</v>
+        <v>79246</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10964,21 +10964,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10988,10 +10988,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>395883</v>
+        <v>395641</v>
       </c>
       <c r="R97" t="n">
-        <v>6804433</v>
+        <v>6804509</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11023,7 +11023,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11033,7 +11033,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11063,7 +11063,7 @@
         <v>131046895</v>
       </c>
       <c r="B98" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11167,10 +11167,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>131033332</v>
+        <v>131046887</v>
       </c>
       <c r="B99" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11202,10 +11202,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>395641</v>
+        <v>395449</v>
       </c>
       <c r="R99" t="n">
-        <v>6804509</v>
+        <v>6804334</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11232,22 +11232,22 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11508,10 +11508,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>131047017</v>
+        <v>131046890</v>
       </c>
       <c r="B102" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11519,39 +11519,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>395448</v>
+        <v>395440</v>
       </c>
       <c r="R102" t="n">
-        <v>6804508</v>
+        <v>6804390</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11583,7 +11578,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11593,19 +11588,14 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>Troliga spår efter tretåig hackspett (barkfälkning)</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD102" t="b">
         <v>0</v>
       </c>
       <c r="AE102" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG102" t="b">
         <v>0</v>
@@ -11625,10 +11615,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>131046796</v>
+        <v>131046952</v>
       </c>
       <c r="B103" t="n">
-        <v>79003</v>
+        <v>79246</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11636,21 +11626,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11660,10 +11650,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>395443</v>
+        <v>395461</v>
       </c>
       <c r="R103" t="n">
-        <v>6804347</v>
+        <v>6804521</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11695,7 +11685,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11705,7 +11695,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11732,10 +11722,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>131046876</v>
+        <v>131046951</v>
       </c>
       <c r="B104" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11767,10 +11757,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>395457</v>
+        <v>395463</v>
       </c>
       <c r="R104" t="n">
-        <v>6804453</v>
+        <v>6804524</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11802,7 +11792,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11812,7 +11802,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11839,10 +11829,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>131046890</v>
+        <v>131046876</v>
       </c>
       <c r="B105" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11874,10 +11864,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>395440</v>
+        <v>395457</v>
       </c>
       <c r="R105" t="n">
-        <v>6804390</v>
+        <v>6804453</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11909,7 +11899,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11919,7 +11909,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11949,7 +11939,7 @@
         <v>131033349</v>
       </c>
       <c r="B106" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12053,10 +12043,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>131046952</v>
+        <v>131047017</v>
       </c>
       <c r="B107" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12064,34 +12054,39 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>395461</v>
+        <v>395448</v>
       </c>
       <c r="R107" t="n">
-        <v>6804521</v>
+        <v>6804508</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12123,7 +12118,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12133,14 +12128,19 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Troliga spår efter tretåig hackspett (barkfälkning)</t>
         </is>
       </c>
       <c r="AD107" t="b">
         <v>0</v>
       </c>
       <c r="AE107" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG107" t="b">
         <v>0</v>
@@ -12160,10 +12160,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>131046951</v>
+        <v>131046796</v>
       </c>
       <c r="B108" t="n">
-        <v>79245</v>
+        <v>79004</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12171,21 +12171,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12195,10 +12195,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>395463</v>
+        <v>395443</v>
       </c>
       <c r="R108" t="n">
-        <v>6804524</v>
+        <v>6804347</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12230,7 +12230,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12240,7 +12240,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12267,10 +12267,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>131033341</v>
+        <v>131046903</v>
       </c>
       <c r="B109" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12302,10 +12302,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>395797</v>
+        <v>395384</v>
       </c>
       <c r="R109" t="n">
-        <v>6804591</v>
+        <v>6804564</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12332,22 +12332,22 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12377,7 +12377,7 @@
         <v>131046957</v>
       </c>
       <c r="B110" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12481,10 +12481,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>131046903</v>
+        <v>131033341</v>
       </c>
       <c r="B111" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12516,10 +12516,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>395384</v>
+        <v>395797</v>
       </c>
       <c r="R111" t="n">
-        <v>6804564</v>
+        <v>6804591</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12546,22 +12546,22 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD111" t="b">

--- a/artfynd/A 28856-2025 artfynd.xlsx
+++ b/artfynd/A 28856-2025 artfynd.xlsx
@@ -2193,10 +2193,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131046868</v>
+        <v>131033283</v>
       </c>
       <c r="B16" t="n">
-        <v>79246</v>
+        <v>79278</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2204,21 +2204,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2228,10 +2228,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>395462</v>
+        <v>395745</v>
       </c>
       <c r="R16" t="n">
-        <v>6804496</v>
+        <v>6804404</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2258,22 +2258,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2300,7 +2300,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131046901</v>
+        <v>131033331</v>
       </c>
       <c r="B17" t="n">
         <v>79246</v>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>395395</v>
+        <v>395707</v>
       </c>
       <c r="R17" t="n">
-        <v>6804547</v>
+        <v>6804307</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2365,22 +2365,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2407,7 +2407,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131033348</v>
+        <v>131046901</v>
       </c>
       <c r="B18" t="n">
         <v>79246</v>
@@ -2442,10 +2442,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>395756</v>
+        <v>395395</v>
       </c>
       <c r="R18" t="n">
-        <v>6804343</v>
+        <v>6804547</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2472,22 +2472,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2728,10 +2728,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131046777</v>
+        <v>131033348</v>
       </c>
       <c r="B21" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2739,39 +2739,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>395435</v>
+        <v>395756</v>
       </c>
       <c r="R21" t="n">
-        <v>6804481</v>
+        <v>6804343</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2798,27 +2793,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:46</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2845,10 +2835,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131047009</v>
+        <v>131046868</v>
       </c>
       <c r="B22" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2856,42 +2846,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>395494</v>
+        <v>395462</v>
       </c>
       <c r="R22" t="n">
-        <v>6804551</v>
+        <v>6804496</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2923,7 +2905,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2933,12 +2915,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:26</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Nästan helt avbarkad klen gran</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2965,10 +2942,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131033283</v>
+        <v>131046777</v>
       </c>
       <c r="B23" t="n">
-        <v>79278</v>
+        <v>57884</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2976,34 +2953,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>395745</v>
+        <v>395435</v>
       </c>
       <c r="R23" t="n">
-        <v>6804404</v>
+        <v>6804481</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3030,22 +3012,27 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3072,10 +3059,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131033331</v>
+        <v>131047009</v>
       </c>
       <c r="B24" t="n">
-        <v>79246</v>
+        <v>57884</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3083,34 +3070,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>395707</v>
+        <v>395494</v>
       </c>
       <c r="R24" t="n">
-        <v>6804307</v>
+        <v>6804551</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3137,22 +3132,27 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Nästan helt avbarkad klen gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3510,10 +3510,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131046894</v>
+        <v>131033302</v>
       </c>
       <c r="B28" t="n">
-        <v>79246</v>
+        <v>79004</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3521,21 +3521,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3545,10 +3545,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>395429</v>
+        <v>395679</v>
       </c>
       <c r="R28" t="n">
-        <v>6804421</v>
+        <v>6804524</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3575,22 +3575,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3617,10 +3617,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131033302</v>
+        <v>131046894</v>
       </c>
       <c r="B29" t="n">
-        <v>79004</v>
+        <v>79246</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3628,21 +3628,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3652,10 +3652,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>395679</v>
+        <v>395429</v>
       </c>
       <c r="R29" t="n">
-        <v>6804524</v>
+        <v>6804421</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3682,22 +3682,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4478,7 +4478,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131046855</v>
+        <v>131046897</v>
       </c>
       <c r="B37" t="n">
         <v>79246</v>
@@ -4513,10 +4513,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>395570</v>
+        <v>395414</v>
       </c>
       <c r="R37" t="n">
-        <v>6804306</v>
+        <v>6804483</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4548,7 +4548,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4558,7 +4558,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4585,7 +4585,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131046897</v>
+        <v>131046855</v>
       </c>
       <c r="B38" t="n">
         <v>79246</v>
@@ -4620,10 +4620,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>395414</v>
+        <v>395570</v>
       </c>
       <c r="R38" t="n">
-        <v>6804483</v>
+        <v>6804306</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4655,7 +4655,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4665,7 +4665,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4799,10 +4799,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131033288</v>
+        <v>131046881</v>
       </c>
       <c r="B40" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4810,39 +4810,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>395651</v>
+        <v>395494</v>
       </c>
       <c r="R40" t="n">
-        <v>6804457</v>
+        <v>6804395</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4869,27 +4864,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:42</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4916,10 +4906,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131046748</v>
+        <v>131033334</v>
       </c>
       <c r="B41" t="n">
-        <v>57881</v>
+        <v>79246</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4927,39 +4917,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>395453</v>
+        <v>395718</v>
       </c>
       <c r="R41" t="n">
-        <v>6804322</v>
+        <v>6804558</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4986,22 +4971,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5028,7 +5013,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131046881</v>
+        <v>131046999</v>
       </c>
       <c r="B42" t="n">
         <v>79246</v>
@@ -5063,10 +5048,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>395494</v>
+        <v>395485</v>
       </c>
       <c r="R42" t="n">
-        <v>6804395</v>
+        <v>6804561</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5098,7 +5083,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5108,7 +5093,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5135,7 +5120,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131033334</v>
+        <v>131046859</v>
       </c>
       <c r="B43" t="n">
         <v>79246</v>
@@ -5170,10 +5155,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>395718</v>
+        <v>395566</v>
       </c>
       <c r="R43" t="n">
-        <v>6804558</v>
+        <v>6804349</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5200,22 +5185,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5242,10 +5227,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131046999</v>
+        <v>131046805</v>
       </c>
       <c r="B44" t="n">
-        <v>79246</v>
+        <v>79003</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5253,21 +5238,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5277,10 +5262,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>395485</v>
+        <v>395461</v>
       </c>
       <c r="R44" t="n">
-        <v>6804561</v>
+        <v>6804539</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5312,7 +5297,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5322,7 +5307,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5349,7 +5334,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131046859</v>
+        <v>131033346</v>
       </c>
       <c r="B45" t="n">
         <v>79246</v>
@@ -5384,10 +5369,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>395566</v>
+        <v>395744</v>
       </c>
       <c r="R45" t="n">
-        <v>6804349</v>
+        <v>6804417</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5414,22 +5399,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5456,10 +5441,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131046805</v>
+        <v>131033288</v>
       </c>
       <c r="B46" t="n">
-        <v>79003</v>
+        <v>57884</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5467,34 +5452,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>395461</v>
+        <v>395651</v>
       </c>
       <c r="R46" t="n">
-        <v>6804539</v>
+        <v>6804457</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5521,22 +5511,27 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5563,10 +5558,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131033346</v>
+        <v>131046748</v>
       </c>
       <c r="B47" t="n">
-        <v>79246</v>
+        <v>57881</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5574,34 +5569,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>395744</v>
+        <v>395453</v>
       </c>
       <c r="R47" t="n">
-        <v>6804417</v>
+        <v>6804322</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5628,22 +5628,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -7061,10 +7061,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131046888</v>
+        <v>131046713</v>
       </c>
       <c r="B61" t="n">
-        <v>79246</v>
+        <v>83226</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7072,21 +7072,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7096,10 +7096,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>395436</v>
+        <v>395454</v>
       </c>
       <c r="R61" t="n">
-        <v>6804373</v>
+        <v>6804501</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7131,7 +7131,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7141,7 +7141,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7168,10 +7168,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131046713</v>
+        <v>131046888</v>
       </c>
       <c r="B62" t="n">
-        <v>83226</v>
+        <v>79246</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7179,21 +7179,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7203,10 +7203,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>395454</v>
+        <v>395436</v>
       </c>
       <c r="R62" t="n">
-        <v>6804501</v>
+        <v>6804373</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7238,7 +7238,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7248,7 +7248,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7382,10 +7382,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131033321</v>
+        <v>131046789</v>
       </c>
       <c r="B64" t="n">
-        <v>79246</v>
+        <v>57884</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7393,34 +7393,39 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>395718</v>
+        <v>395495</v>
       </c>
       <c r="R64" t="n">
-        <v>6804573</v>
+        <v>6804385</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7447,22 +7452,27 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>09:59</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7489,7 +7499,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131046882</v>
+        <v>131033321</v>
       </c>
       <c r="B65" t="n">
         <v>79246</v>
@@ -7524,10 +7534,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>395493</v>
+        <v>395718</v>
       </c>
       <c r="R65" t="n">
-        <v>6804376</v>
+        <v>6804573</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7554,22 +7564,22 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7596,7 +7606,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131033327</v>
+        <v>131046882</v>
       </c>
       <c r="B66" t="n">
         <v>79246</v>
@@ -7631,10 +7641,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>395671</v>
+        <v>395493</v>
       </c>
       <c r="R66" t="n">
-        <v>6804435</v>
+        <v>6804376</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7661,22 +7671,22 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7703,7 +7713,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131033326</v>
+        <v>131033327</v>
       </c>
       <c r="B67" t="n">
         <v>79246</v>
@@ -7738,10 +7748,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>395665</v>
+        <v>395671</v>
       </c>
       <c r="R67" t="n">
-        <v>6804439</v>
+        <v>6804435</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7773,7 +7783,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7783,7 +7793,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7810,10 +7820,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131046789</v>
+        <v>131033326</v>
       </c>
       <c r="B68" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7821,39 +7831,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>395495</v>
+        <v>395665</v>
       </c>
       <c r="R68" t="n">
-        <v>6804385</v>
+        <v>6804439</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7880,27 +7885,22 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>09:59</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8579,10 +8579,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131046865</v>
+        <v>131033303</v>
       </c>
       <c r="B75" t="n">
-        <v>79246</v>
+        <v>79004</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8590,21 +8590,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8614,10 +8614,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>395546</v>
+        <v>395706</v>
       </c>
       <c r="R75" t="n">
-        <v>6804405</v>
+        <v>6804535</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8644,22 +8644,22 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8686,7 +8686,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131046862</v>
+        <v>131046865</v>
       </c>
       <c r="B76" t="n">
         <v>79246</v>
@@ -8721,10 +8721,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>395554</v>
+        <v>395546</v>
       </c>
       <c r="R76" t="n">
-        <v>6804375</v>
+        <v>6804405</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8756,7 +8756,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8766,7 +8766,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8793,7 +8793,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131046886</v>
+        <v>131046862</v>
       </c>
       <c r="B77" t="n">
         <v>79246</v>
@@ -8828,10 +8828,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>395447</v>
+        <v>395554</v>
       </c>
       <c r="R77" t="n">
-        <v>6804315</v>
+        <v>6804375</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8863,7 +8863,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8873,7 +8873,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8900,10 +8900,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131033303</v>
+        <v>131046886</v>
       </c>
       <c r="B78" t="n">
-        <v>79004</v>
+        <v>79246</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8911,21 +8911,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8935,10 +8935,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>395706</v>
+        <v>395447</v>
       </c>
       <c r="R78" t="n">
-        <v>6804535</v>
+        <v>6804315</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8965,22 +8965,22 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9007,7 +9007,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131046854</v>
+        <v>131046857</v>
       </c>
       <c r="B79" t="n">
         <v>79246</v>
@@ -9042,10 +9042,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>395579</v>
+        <v>395560</v>
       </c>
       <c r="R79" t="n">
-        <v>6804294</v>
+        <v>6804326</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9077,7 +9077,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9087,7 +9087,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9114,7 +9114,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131033330</v>
+        <v>131046854</v>
       </c>
       <c r="B80" t="n">
         <v>79246</v>
@@ -9149,10 +9149,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>395702</v>
+        <v>395579</v>
       </c>
       <c r="R80" t="n">
-        <v>6804325</v>
+        <v>6804294</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9179,22 +9179,22 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9221,7 +9221,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>131033322</v>
+        <v>131033330</v>
       </c>
       <c r="B81" t="n">
         <v>79246</v>
@@ -9256,10 +9256,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>395692</v>
+        <v>395702</v>
       </c>
       <c r="R81" t="n">
-        <v>6804550</v>
+        <v>6804325</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9291,7 +9291,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9301,7 +9301,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9328,7 +9328,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>131046883</v>
+        <v>131033322</v>
       </c>
       <c r="B82" t="n">
         <v>79246</v>
@@ -9363,10 +9363,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>395494</v>
+        <v>395692</v>
       </c>
       <c r="R82" t="n">
-        <v>6804367</v>
+        <v>6804550</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9393,22 +9393,22 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9435,7 +9435,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>131046889</v>
+        <v>131046883</v>
       </c>
       <c r="B83" t="n">
         <v>79246</v>
@@ -9470,10 +9470,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>395429</v>
+        <v>395494</v>
       </c>
       <c r="R83" t="n">
-        <v>6804384</v>
+        <v>6804367</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9505,7 +9505,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9515,7 +9515,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9542,7 +9542,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>131046857</v>
+        <v>131046889</v>
       </c>
       <c r="B84" t="n">
         <v>79246</v>
@@ -9577,10 +9577,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>395560</v>
+        <v>395429</v>
       </c>
       <c r="R84" t="n">
-        <v>6804326</v>
+        <v>6804384</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9612,7 +9612,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9622,7 +9622,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10418,7 +10418,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>131046950</v>
+        <v>131046870</v>
       </c>
       <c r="B92" t="n">
         <v>79246</v>
@@ -10453,10 +10453,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>395470</v>
+        <v>395450</v>
       </c>
       <c r="R92" t="n">
-        <v>6804530</v>
+        <v>6804507</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10488,7 +10488,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10498,7 +10498,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10525,7 +10525,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>131033345</v>
+        <v>131046992</v>
       </c>
       <c r="B93" t="n">
         <v>79246</v>
@@ -10560,10 +10560,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>395748</v>
+        <v>395477</v>
       </c>
       <c r="R93" t="n">
-        <v>6804429</v>
+        <v>6804563</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10590,22 +10590,22 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10632,7 +10632,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>131046870</v>
+        <v>131046950</v>
       </c>
       <c r="B94" t="n">
         <v>79246</v>
@@ -10667,10 +10667,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>395450</v>
+        <v>395470</v>
       </c>
       <c r="R94" t="n">
-        <v>6804507</v>
+        <v>6804530</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10702,7 +10702,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10712,7 +10712,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10739,7 +10739,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>131046992</v>
+        <v>131033345</v>
       </c>
       <c r="B95" t="n">
         <v>79246</v>
@@ -10774,10 +10774,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>395477</v>
+        <v>395748</v>
       </c>
       <c r="R95" t="n">
-        <v>6804563</v>
+        <v>6804429</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10804,22 +10804,22 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10953,7 +10953,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>131033332</v>
+        <v>131046895</v>
       </c>
       <c r="B97" t="n">
         <v>79246</v>
@@ -10988,10 +10988,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>395641</v>
+        <v>395436</v>
       </c>
       <c r="R97" t="n">
-        <v>6804509</v>
+        <v>6804436</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11018,22 +11018,22 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11060,7 +11060,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>131046895</v>
+        <v>131046887</v>
       </c>
       <c r="B98" t="n">
         <v>79246</v>
@@ -11095,10 +11095,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>395436</v>
+        <v>395449</v>
       </c>
       <c r="R98" t="n">
-        <v>6804436</v>
+        <v>6804334</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11130,7 +11130,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11140,7 +11140,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11167,10 +11167,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>131046887</v>
+        <v>131046780</v>
       </c>
       <c r="B99" t="n">
-        <v>79246</v>
+        <v>57884</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11178,34 +11178,39 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>395449</v>
+        <v>395470</v>
       </c>
       <c r="R99" t="n">
-        <v>6804334</v>
+        <v>6804530</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11237,7 +11242,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11247,7 +11252,12 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11274,7 +11284,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>131046780</v>
+        <v>131047019</v>
       </c>
       <c r="B100" t="n">
         <v>57884</v>
@@ -11305,7 +11315,7 @@
       <c r="I100" t="inlineStr"/>
       <c r="M100" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
@@ -11314,10 +11324,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>395470</v>
+        <v>395446</v>
       </c>
       <c r="R100" t="n">
-        <v>6804530</v>
+        <v>6804531</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11349,7 +11359,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11359,19 +11369,19 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>Äldre ringhack (gran)</t>
+          <t>Troliga spår efter tretåig hackspett (barkfälkning)</t>
         </is>
       </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
       <c r="AE100" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG100" t="b">
         <v>0</v>
@@ -11391,10 +11401,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>131047019</v>
+        <v>131033332</v>
       </c>
       <c r="B101" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11402,39 +11412,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>395446</v>
+        <v>395641</v>
       </c>
       <c r="R101" t="n">
-        <v>6804531</v>
+        <v>6804509</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11461,34 +11466,29 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>11:44</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>Troliga spår efter tretåig hackspett (barkfälkning)</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD101" t="b">
         <v>0</v>
       </c>
       <c r="AE101" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG101" t="b">
         <v>0</v>
@@ -11508,7 +11508,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>131046890</v>
+        <v>131046952</v>
       </c>
       <c r="B102" t="n">
         <v>79246</v>
@@ -11543,10 +11543,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>395440</v>
+        <v>395461</v>
       </c>
       <c r="R102" t="n">
-        <v>6804390</v>
+        <v>6804521</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11578,7 +11578,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11615,7 +11615,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>131046952</v>
+        <v>131046951</v>
       </c>
       <c r="B103" t="n">
         <v>79246</v>
@@ -11650,10 +11650,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>395461</v>
+        <v>395463</v>
       </c>
       <c r="R103" t="n">
-        <v>6804521</v>
+        <v>6804524</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11722,7 +11722,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>131046951</v>
+        <v>131046876</v>
       </c>
       <c r="B104" t="n">
         <v>79246</v>
@@ -11757,10 +11757,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>395463</v>
+        <v>395457</v>
       </c>
       <c r="R104" t="n">
-        <v>6804524</v>
+        <v>6804453</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11792,7 +11792,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11802,7 +11802,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11829,7 +11829,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>131046876</v>
+        <v>131033349</v>
       </c>
       <c r="B105" t="n">
         <v>79246</v>
@@ -11864,10 +11864,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>395457</v>
+        <v>395757</v>
       </c>
       <c r="R105" t="n">
-        <v>6804453</v>
+        <v>6804291</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11894,22 +11894,22 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11936,10 +11936,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>131033349</v>
+        <v>131046796</v>
       </c>
       <c r="B106" t="n">
-        <v>79246</v>
+        <v>79004</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11947,21 +11947,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11971,10 +11971,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>395757</v>
+        <v>395443</v>
       </c>
       <c r="R106" t="n">
-        <v>6804291</v>
+        <v>6804347</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12001,22 +12001,22 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12043,10 +12043,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>131047017</v>
+        <v>131046890</v>
       </c>
       <c r="B107" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12054,39 +12054,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>395448</v>
+        <v>395440</v>
       </c>
       <c r="R107" t="n">
-        <v>6804508</v>
+        <v>6804390</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12118,7 +12113,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12128,19 +12123,14 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>Troliga spår efter tretåig hackspett (barkfälkning)</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD107" t="b">
         <v>0</v>
       </c>
       <c r="AE107" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG107" t="b">
         <v>0</v>
@@ -12160,10 +12150,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>131046796</v>
+        <v>131047017</v>
       </c>
       <c r="B108" t="n">
-        <v>79004</v>
+        <v>57884</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12171,34 +12161,39 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>395443</v>
+        <v>395448</v>
       </c>
       <c r="R108" t="n">
-        <v>6804347</v>
+        <v>6804508</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12230,7 +12225,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12240,14 +12235,19 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Troliga spår efter tretåig hackspett (barkfälkning)</t>
         </is>
       </c>
       <c r="AD108" t="b">
         <v>0</v>
       </c>
       <c r="AE108" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG108" t="b">
         <v>0</v>

--- a/artfynd/A 28856-2025 artfynd.xlsx
+++ b/artfynd/A 28856-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131046875</v>
+        <v>131046803</v>
       </c>
       <c r="B2" t="n">
-        <v>79246</v>
+        <v>79005</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>395444</v>
+        <v>395450</v>
       </c>
       <c r="R2" t="n">
-        <v>6804461</v>
+        <v>6804390</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131046803</v>
+        <v>131046747</v>
       </c>
       <c r="B3" t="n">
-        <v>79003</v>
+        <v>57883</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,34 +793,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>395450</v>
+        <v>395480</v>
       </c>
       <c r="R3" t="n">
-        <v>6804390</v>
+        <v>6804496</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131046995</v>
+        <v>131046790</v>
       </c>
       <c r="B4" t="n">
-        <v>79246</v>
+        <v>57886</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,34 +905,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>395491</v>
+        <v>395416</v>
       </c>
       <c r="R4" t="n">
-        <v>6804522</v>
+        <v>6804491</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +979,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131046747</v>
+        <v>131046875</v>
       </c>
       <c r="B5" t="n">
-        <v>57881</v>
+        <v>79248</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,39 +1022,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>395480</v>
+        <v>395444</v>
       </c>
       <c r="R5" t="n">
-        <v>6804496</v>
+        <v>6804461</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1081,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1081,7 +1091,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,7 +1121,7 @@
         <v>131046947</v>
       </c>
       <c r="B6" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1228,7 @@
         <v>131046896</v>
       </c>
       <c r="B7" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1335,7 @@
         <v>131046872</v>
       </c>
       <c r="B8" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1442,7 @@
         <v>131046873</v>
       </c>
       <c r="B9" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1536,10 +1546,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131046790</v>
+        <v>131046995</v>
       </c>
       <c r="B10" t="n">
-        <v>57884</v>
+        <v>79248</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1547,39 +1557,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>395416</v>
+        <v>395491</v>
       </c>
       <c r="R10" t="n">
-        <v>6804491</v>
+        <v>6804522</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1616,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1621,12 +1626,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:27</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1653,10 +1653,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131033342</v>
+        <v>131046749</v>
       </c>
       <c r="B11" t="n">
-        <v>79246</v>
+        <v>57883</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1664,34 +1664,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>395753</v>
+        <v>395449</v>
       </c>
       <c r="R11" t="n">
-        <v>6804557</v>
+        <v>6804395</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1718,22 +1723,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1760,10 +1765,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131046858</v>
+        <v>131046884</v>
       </c>
       <c r="B12" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1795,10 +1800,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>395570</v>
+        <v>395489</v>
       </c>
       <c r="R12" t="n">
-        <v>6804341</v>
+        <v>6804292</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1830,7 +1835,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1840,7 +1845,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1867,10 +1872,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131046749</v>
+        <v>131046858</v>
       </c>
       <c r="B13" t="n">
-        <v>57881</v>
+        <v>79248</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1878,39 +1883,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>395449</v>
+        <v>395570</v>
       </c>
       <c r="R13" t="n">
-        <v>6804395</v>
+        <v>6804341</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1979,10 +1979,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131046884</v>
+        <v>131033342</v>
       </c>
       <c r="B14" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2014,10 +2014,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>395489</v>
+        <v>395753</v>
       </c>
       <c r="R14" t="n">
-        <v>6804292</v>
+        <v>6804557</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2044,22 +2044,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2089,7 +2089,7 @@
         <v>131046807</v>
       </c>
       <c r="B15" t="n">
-        <v>83209</v>
+        <v>83211</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2193,10 +2193,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131033283</v>
+        <v>131033331</v>
       </c>
       <c r="B16" t="n">
-        <v>79278</v>
+        <v>79248</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2204,21 +2204,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2228,10 +2228,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>395745</v>
+        <v>395707</v>
       </c>
       <c r="R16" t="n">
-        <v>6804404</v>
+        <v>6804307</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2300,10 +2300,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131033331</v>
+        <v>131046955</v>
       </c>
       <c r="B17" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>395707</v>
+        <v>395432</v>
       </c>
       <c r="R17" t="n">
-        <v>6804307</v>
+        <v>6804533</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2365,22 +2365,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2410,7 +2410,7 @@
         <v>131046901</v>
       </c>
       <c r="B18" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2514,10 +2514,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131046955</v>
+        <v>131046878</v>
       </c>
       <c r="B19" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2549,10 +2549,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>395432</v>
+        <v>395478</v>
       </c>
       <c r="R19" t="n">
-        <v>6804533</v>
+        <v>6804426</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2584,7 +2584,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2594,7 +2594,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2621,10 +2621,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131046878</v>
+        <v>131046868</v>
       </c>
       <c r="B20" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2656,10 +2656,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>395478</v>
+        <v>395462</v>
       </c>
       <c r="R20" t="n">
-        <v>6804426</v>
+        <v>6804496</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2731,7 +2731,7 @@
         <v>131033348</v>
       </c>
       <c r="B21" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2835,10 +2835,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131046868</v>
+        <v>131033283</v>
       </c>
       <c r="B22" t="n">
-        <v>79246</v>
+        <v>79280</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2846,21 +2846,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2870,10 +2870,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>395462</v>
+        <v>395745</v>
       </c>
       <c r="R22" t="n">
-        <v>6804496</v>
+        <v>6804404</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2900,22 +2900,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2945,7 +2945,7 @@
         <v>131046777</v>
       </c>
       <c r="B23" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>131047009</v>
       </c>
       <c r="B24" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3179,10 +3179,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131033324</v>
+        <v>131033294</v>
       </c>
       <c r="B25" t="n">
-        <v>79246</v>
+        <v>57886</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3190,34 +3190,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>395676</v>
+        <v>395714</v>
       </c>
       <c r="R25" t="n">
-        <v>6804490</v>
+        <v>6804552</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3249,7 +3254,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3259,7 +3264,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3286,10 +3296,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131033294</v>
+        <v>131033302</v>
       </c>
       <c r="B26" t="n">
-        <v>57884</v>
+        <v>79006</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3297,39 +3307,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>395714</v>
+        <v>395679</v>
       </c>
       <c r="R26" t="n">
-        <v>6804552</v>
+        <v>6804524</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3361,7 +3366,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3371,12 +3376,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:06</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3403,10 +3403,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131033344</v>
+        <v>131033324</v>
       </c>
       <c r="B27" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3438,10 +3438,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>395753</v>
+        <v>395676</v>
       </c>
       <c r="R27" t="n">
-        <v>6804482</v>
+        <v>6804490</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3473,7 +3473,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3483,7 +3483,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3510,10 +3510,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131033302</v>
+        <v>131046894</v>
       </c>
       <c r="B28" t="n">
-        <v>79004</v>
+        <v>79248</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3521,21 +3521,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3545,10 +3545,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>395679</v>
+        <v>395429</v>
       </c>
       <c r="R28" t="n">
-        <v>6804524</v>
+        <v>6804421</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3575,22 +3575,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3617,10 +3617,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131046894</v>
+        <v>131033344</v>
       </c>
       <c r="B29" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3652,10 +3652,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>395429</v>
+        <v>395753</v>
       </c>
       <c r="R29" t="n">
-        <v>6804421</v>
+        <v>6804482</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3682,22 +3682,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3724,50 +3724,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131047035</v>
+        <v>131046892</v>
       </c>
       <c r="B30" t="n">
-        <v>5177</v>
+        <v>79248</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>395505</v>
+        <v>395445</v>
       </c>
       <c r="R30" t="n">
-        <v>6804295</v>
+        <v>6804404</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3799,7 +3794,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3809,7 +3804,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3836,10 +3831,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131046994</v>
+        <v>131046998</v>
       </c>
       <c r="B31" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3871,10 +3866,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>395484</v>
+        <v>395494</v>
       </c>
       <c r="R31" t="n">
-        <v>6804534</v>
+        <v>6804551</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3906,7 +3901,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3916,7 +3911,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3943,10 +3938,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131046885</v>
+        <v>131046994</v>
       </c>
       <c r="B32" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3978,10 +3973,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>395486</v>
+        <v>395484</v>
       </c>
       <c r="R32" t="n">
-        <v>6804289</v>
+        <v>6804534</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4013,7 +4008,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4023,7 +4018,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4050,45 +4045,50 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131046956</v>
+        <v>131047035</v>
       </c>
       <c r="B33" t="n">
-        <v>79246</v>
+        <v>5177</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>395418</v>
+        <v>395505</v>
       </c>
       <c r="R33" t="n">
-        <v>6804552</v>
+        <v>6804295</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4130,7 +4130,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4157,10 +4157,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131046892</v>
+        <v>131046885</v>
       </c>
       <c r="B34" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4192,10 +4192,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>395445</v>
+        <v>395486</v>
       </c>
       <c r="R34" t="n">
-        <v>6804404</v>
+        <v>6804289</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4237,7 +4237,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4264,10 +4264,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131046898</v>
+        <v>131046956</v>
       </c>
       <c r="B35" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4299,10 +4299,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>395393</v>
+        <v>395418</v>
       </c>
       <c r="R35" t="n">
-        <v>6804503</v>
+        <v>6804552</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4344,7 +4344,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4371,10 +4371,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131046998</v>
+        <v>131046898</v>
       </c>
       <c r="B36" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4406,10 +4406,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>395494</v>
+        <v>395393</v>
       </c>
       <c r="R36" t="n">
-        <v>6804551</v>
+        <v>6804503</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4478,10 +4478,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131046897</v>
+        <v>131046855</v>
       </c>
       <c r="B37" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4513,10 +4513,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>395414</v>
+        <v>395570</v>
       </c>
       <c r="R37" t="n">
-        <v>6804483</v>
+        <v>6804306</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4548,7 +4548,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4558,7 +4558,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4585,10 +4585,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131046855</v>
+        <v>131046897</v>
       </c>
       <c r="B38" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4620,10 +4620,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>395570</v>
+        <v>395414</v>
       </c>
       <c r="R38" t="n">
-        <v>6804306</v>
+        <v>6804483</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4655,7 +4655,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4665,7 +4665,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4695,7 +4695,7 @@
         <v>131033347</v>
       </c>
       <c r="B39" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4799,10 +4799,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131046881</v>
+        <v>131046748</v>
       </c>
       <c r="B40" t="n">
-        <v>79246</v>
+        <v>57883</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4810,34 +4810,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>395494</v>
+        <v>395453</v>
       </c>
       <c r="R40" t="n">
-        <v>6804395</v>
+        <v>6804322</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4869,7 +4874,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4879,7 +4884,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4906,10 +4911,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131033334</v>
+        <v>131046881</v>
       </c>
       <c r="B41" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4941,10 +4946,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>395718</v>
+        <v>395494</v>
       </c>
       <c r="R41" t="n">
-        <v>6804558</v>
+        <v>6804395</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4971,22 +4976,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5016,7 +5021,7 @@
         <v>131046999</v>
       </c>
       <c r="B42" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5123,7 +5128,7 @@
         <v>131046859</v>
       </c>
       <c r="B43" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5230,7 +5235,7 @@
         <v>131046805</v>
       </c>
       <c r="B44" t="n">
-        <v>79003</v>
+        <v>79005</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5334,10 +5339,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131033346</v>
+        <v>131033334</v>
       </c>
       <c r="B45" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5369,10 +5374,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>395744</v>
+        <v>395718</v>
       </c>
       <c r="R45" t="n">
-        <v>6804417</v>
+        <v>6804558</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5404,7 +5409,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5414,7 +5419,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5441,10 +5446,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131033288</v>
+        <v>131033346</v>
       </c>
       <c r="B46" t="n">
-        <v>57884</v>
+        <v>79248</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5452,39 +5457,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>395651</v>
+        <v>395744</v>
       </c>
       <c r="R46" t="n">
-        <v>6804457</v>
+        <v>6804417</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5526,12 +5526,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:42</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5558,10 +5553,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131046748</v>
+        <v>131033288</v>
       </c>
       <c r="B47" t="n">
-        <v>57881</v>
+        <v>57886</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5569,16 +5564,16 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -5598,10 +5593,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>395453</v>
+        <v>395651</v>
       </c>
       <c r="R47" t="n">
-        <v>6804322</v>
+        <v>6804457</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5628,22 +5623,27 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5670,10 +5670,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131046866</v>
+        <v>131046948</v>
       </c>
       <c r="B48" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5705,10 +5705,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>395542</v>
+        <v>395462</v>
       </c>
       <c r="R48" t="n">
-        <v>6804432</v>
+        <v>6804542</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5750,7 +5750,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5777,10 +5777,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131046954</v>
+        <v>131046712</v>
       </c>
       <c r="B49" t="n">
-        <v>79246</v>
+        <v>83228</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5788,21 +5788,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5812,10 +5812,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>395446</v>
+        <v>395468</v>
       </c>
       <c r="R49" t="n">
-        <v>6804531</v>
+        <v>6804494</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5847,7 +5847,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5857,7 +5857,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5884,10 +5884,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131046997</v>
+        <v>131046949</v>
       </c>
       <c r="B50" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5919,10 +5919,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>395518</v>
+        <v>395463</v>
       </c>
       <c r="R50" t="n">
-        <v>6804527</v>
+        <v>6804534</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5954,7 +5954,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5964,7 +5964,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5991,10 +5991,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131046861</v>
+        <v>131046869</v>
       </c>
       <c r="B51" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6026,10 +6026,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>395564</v>
+        <v>395456</v>
       </c>
       <c r="R51" t="n">
-        <v>6804373</v>
+        <v>6804500</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6061,7 +6061,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6071,7 +6071,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6098,10 +6098,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131033323</v>
+        <v>131046954</v>
       </c>
       <c r="B52" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6133,10 +6133,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>395680</v>
+        <v>395446</v>
       </c>
       <c r="R52" t="n">
-        <v>6804541</v>
+        <v>6804531</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6163,22 +6163,22 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6205,10 +6205,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131033352</v>
+        <v>131046997</v>
       </c>
       <c r="B53" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6240,10 +6240,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>395857</v>
+        <v>395518</v>
       </c>
       <c r="R53" t="n">
-        <v>6804292</v>
+        <v>6804527</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6270,22 +6270,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6312,10 +6312,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131046949</v>
+        <v>131046861</v>
       </c>
       <c r="B54" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6347,10 +6347,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>395463</v>
+        <v>395564</v>
       </c>
       <c r="R54" t="n">
-        <v>6804534</v>
+        <v>6804373</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6382,7 +6382,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6392,7 +6392,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6419,10 +6419,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131046948</v>
+        <v>131033323</v>
       </c>
       <c r="B55" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6454,10 +6454,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>395462</v>
+        <v>395680</v>
       </c>
       <c r="R55" t="n">
-        <v>6804542</v>
+        <v>6804541</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6484,22 +6484,22 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6526,10 +6526,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131046880</v>
+        <v>131033352</v>
       </c>
       <c r="B56" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6561,10 +6561,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>395491</v>
+        <v>395857</v>
       </c>
       <c r="R56" t="n">
-        <v>6804393</v>
+        <v>6804292</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6591,22 +6591,22 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6633,10 +6633,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131046869</v>
+        <v>131046866</v>
       </c>
       <c r="B57" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6668,10 +6668,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>395456</v>
+        <v>395542</v>
       </c>
       <c r="R57" t="n">
-        <v>6804500</v>
+        <v>6804432</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6703,7 +6703,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6713,7 +6713,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6740,10 +6740,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131046712</v>
+        <v>131046880</v>
       </c>
       <c r="B58" t="n">
-        <v>83226</v>
+        <v>79248</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6751,21 +6751,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6775,10 +6775,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>395468</v>
+        <v>395491</v>
       </c>
       <c r="R58" t="n">
-        <v>6804494</v>
+        <v>6804393</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6810,7 +6810,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6820,7 +6820,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6847,10 +6847,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131046879</v>
+        <v>131046874</v>
       </c>
       <c r="B59" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6882,10 +6882,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>395482</v>
+        <v>395433</v>
       </c>
       <c r="R59" t="n">
-        <v>6804421</v>
+        <v>6804469</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6917,7 +6917,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6954,10 +6954,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131046874</v>
+        <v>131046879</v>
       </c>
       <c r="B60" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6989,10 +6989,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>395433</v>
+        <v>395482</v>
       </c>
       <c r="R60" t="n">
-        <v>6804469</v>
+        <v>6804421</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7024,7 +7024,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7064,7 +7064,7 @@
         <v>131046713</v>
       </c>
       <c r="B61" t="n">
-        <v>83226</v>
+        <v>83228</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7171,7 +7171,7 @@
         <v>131046888</v>
       </c>
       <c r="B62" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7275,10 +7275,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131046996</v>
+        <v>131033321</v>
       </c>
       <c r="B63" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7310,10 +7310,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>395485</v>
+        <v>395718</v>
       </c>
       <c r="R63" t="n">
-        <v>6804506</v>
+        <v>6804573</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7340,22 +7340,22 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7382,10 +7382,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131046789</v>
+        <v>131046882</v>
       </c>
       <c r="B64" t="n">
-        <v>57884</v>
+        <v>79248</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7393,39 +7393,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>395495</v>
+        <v>395493</v>
       </c>
       <c r="R64" t="n">
-        <v>6804385</v>
+        <v>6804376</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7457,7 +7452,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7467,12 +7462,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>09:59</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7499,10 +7489,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131033321</v>
+        <v>131033327</v>
       </c>
       <c r="B65" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7534,10 +7524,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>395718</v>
+        <v>395671</v>
       </c>
       <c r="R65" t="n">
-        <v>6804573</v>
+        <v>6804435</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7569,7 +7559,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7579,7 +7569,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7606,10 +7596,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131046882</v>
+        <v>131033326</v>
       </c>
       <c r="B66" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7641,10 +7631,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>395493</v>
+        <v>395665</v>
       </c>
       <c r="R66" t="n">
-        <v>6804376</v>
+        <v>6804439</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7671,22 +7661,22 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7713,10 +7703,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131033327</v>
+        <v>131046996</v>
       </c>
       <c r="B67" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7748,10 +7738,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>395671</v>
+        <v>395485</v>
       </c>
       <c r="R67" t="n">
-        <v>6804435</v>
+        <v>6804506</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7778,22 +7768,22 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7820,10 +7810,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131033326</v>
+        <v>131046789</v>
       </c>
       <c r="B68" t="n">
-        <v>79246</v>
+        <v>57886</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7831,34 +7821,39 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>395665</v>
+        <v>395495</v>
       </c>
       <c r="R68" t="n">
-        <v>6804439</v>
+        <v>6804385</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7885,22 +7880,27 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>09:59</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7927,32 +7927,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131046993</v>
+        <v>131033299</v>
       </c>
       <c r="B69" t="n">
-        <v>79246</v>
+        <v>79272</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7962,10 +7962,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>395472</v>
+        <v>395890</v>
       </c>
       <c r="R69" t="n">
-        <v>6804550</v>
+        <v>6804464</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7992,22 +7992,22 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8034,10 +8034,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131033353</v>
+        <v>131046993</v>
       </c>
       <c r="B70" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8069,10 +8069,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>395859</v>
+        <v>395472</v>
       </c>
       <c r="R70" t="n">
-        <v>6804312</v>
+        <v>6804550</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8099,22 +8099,22 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8141,10 +8141,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131046856</v>
+        <v>131033353</v>
       </c>
       <c r="B71" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8176,10 +8176,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>395564</v>
+        <v>395859</v>
       </c>
       <c r="R71" t="n">
-        <v>6804311</v>
+        <v>6804312</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8206,22 +8206,22 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8248,10 +8248,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131046877</v>
+        <v>131046856</v>
       </c>
       <c r="B72" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8283,10 +8283,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>395464</v>
+        <v>395564</v>
       </c>
       <c r="R72" t="n">
-        <v>6804442</v>
+        <v>6804311</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8318,7 +8318,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8328,7 +8328,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8355,10 +8355,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131033295</v>
+        <v>131046877</v>
       </c>
       <c r="B73" t="n">
-        <v>57884</v>
+        <v>79248</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8366,39 +8366,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>395744</v>
+        <v>395464</v>
       </c>
       <c r="R73" t="n">
-        <v>6804575</v>
+        <v>6804442</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8425,27 +8420,22 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>13:09</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8472,45 +8462,50 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131033299</v>
+        <v>131033295</v>
       </c>
       <c r="B74" t="n">
-        <v>79270</v>
+        <v>57886</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6434</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>395890</v>
+        <v>395744</v>
       </c>
       <c r="R74" t="n">
-        <v>6804464</v>
+        <v>6804575</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8542,7 +8537,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8552,7 +8547,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8582,7 +8582,7 @@
         <v>131033303</v>
       </c>
       <c r="B75" t="n">
-        <v>79004</v>
+        <v>79006</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8686,10 +8686,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131046865</v>
+        <v>131046886</v>
       </c>
       <c r="B76" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8721,10 +8721,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>395546</v>
+        <v>395447</v>
       </c>
       <c r="R76" t="n">
-        <v>6804405</v>
+        <v>6804315</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8756,7 +8756,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8766,7 +8766,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8796,7 +8796,7 @@
         <v>131046862</v>
       </c>
       <c r="B77" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8900,10 +8900,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131046886</v>
+        <v>131046865</v>
       </c>
       <c r="B78" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8935,10 +8935,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>395447</v>
+        <v>395546</v>
       </c>
       <c r="R78" t="n">
-        <v>6804315</v>
+        <v>6804405</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8970,7 +8970,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9007,10 +9007,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131046857</v>
+        <v>131046854</v>
       </c>
       <c r="B79" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9042,10 +9042,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>395560</v>
+        <v>395579</v>
       </c>
       <c r="R79" t="n">
-        <v>6804326</v>
+        <v>6804294</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9077,7 +9077,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9087,7 +9087,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9114,10 +9114,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131046854</v>
+        <v>131033330</v>
       </c>
       <c r="B80" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9149,10 +9149,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>395579</v>
+        <v>395702</v>
       </c>
       <c r="R80" t="n">
-        <v>6804294</v>
+        <v>6804325</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9179,22 +9179,22 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9221,10 +9221,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>131033330</v>
+        <v>131033322</v>
       </c>
       <c r="B81" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9256,10 +9256,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>395702</v>
+        <v>395692</v>
       </c>
       <c r="R81" t="n">
-        <v>6804325</v>
+        <v>6804550</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9291,7 +9291,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9301,7 +9301,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9328,10 +9328,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>131033322</v>
+        <v>131046883</v>
       </c>
       <c r="B82" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9363,10 +9363,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>395692</v>
+        <v>395494</v>
       </c>
       <c r="R82" t="n">
-        <v>6804550</v>
+        <v>6804367</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9393,22 +9393,22 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9435,10 +9435,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>131046883</v>
+        <v>131046889</v>
       </c>
       <c r="B83" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9470,10 +9470,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>395494</v>
+        <v>395429</v>
       </c>
       <c r="R83" t="n">
-        <v>6804367</v>
+        <v>6804384</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9505,7 +9505,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9515,7 +9515,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9542,10 +9542,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>131046889</v>
+        <v>131046857</v>
       </c>
       <c r="B84" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9577,10 +9577,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>395429</v>
+        <v>395560</v>
       </c>
       <c r="R84" t="n">
-        <v>6804384</v>
+        <v>6804326</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9612,7 +9612,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9622,7 +9622,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9652,7 +9652,7 @@
         <v>131046893</v>
       </c>
       <c r="B85" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9759,7 +9759,7 @@
         <v>131033333</v>
       </c>
       <c r="B86" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9863,10 +9863,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>131046902</v>
+        <v>131046860</v>
       </c>
       <c r="B87" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9898,10 +9898,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>395389</v>
+        <v>395578</v>
       </c>
       <c r="R87" t="n">
-        <v>6804555</v>
+        <v>6804350</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9933,7 +9933,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9943,7 +9943,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9970,10 +9970,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>131046860</v>
+        <v>131046902</v>
       </c>
       <c r="B88" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10005,10 +10005,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>395578</v>
+        <v>395389</v>
       </c>
       <c r="R88" t="n">
-        <v>6804350</v>
+        <v>6804555</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10040,7 +10040,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10050,7 +10050,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10080,7 +10080,7 @@
         <v>131047018</v>
       </c>
       <c r="B89" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10197,7 +10197,7 @@
         <v>131033293</v>
       </c>
       <c r="B90" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10311,10 +10311,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>131046891</v>
+        <v>131046870</v>
       </c>
       <c r="B91" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10346,10 +10346,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>395453</v>
+        <v>395450</v>
       </c>
       <c r="R91" t="n">
-        <v>6804400</v>
+        <v>6804507</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10391,7 +10391,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10418,10 +10418,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>131046870</v>
+        <v>131046891</v>
       </c>
       <c r="B92" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10453,10 +10453,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>395450</v>
+        <v>395453</v>
       </c>
       <c r="R92" t="n">
-        <v>6804507</v>
+        <v>6804400</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10488,7 +10488,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10498,7 +10498,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10525,10 +10525,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>131046992</v>
+        <v>131046950</v>
       </c>
       <c r="B93" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10560,10 +10560,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>395477</v>
+        <v>395470</v>
       </c>
       <c r="R93" t="n">
-        <v>6804563</v>
+        <v>6804530</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10595,7 +10595,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10605,7 +10605,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10632,10 +10632,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>131046950</v>
+        <v>131046992</v>
       </c>
       <c r="B94" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10667,10 +10667,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>395470</v>
+        <v>395477</v>
       </c>
       <c r="R94" t="n">
-        <v>6804530</v>
+        <v>6804563</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10702,7 +10702,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10712,7 +10712,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10742,7 +10742,7 @@
         <v>131033345</v>
       </c>
       <c r="B95" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10846,10 +10846,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>131033362</v>
+        <v>131046887</v>
       </c>
       <c r="B96" t="n">
-        <v>78912</v>
+        <v>79248</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10857,21 +10857,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10881,10 +10881,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>395883</v>
+        <v>395449</v>
       </c>
       <c r="R96" t="n">
-        <v>6804433</v>
+        <v>6804334</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10911,22 +10911,22 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10953,10 +10953,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>131046895</v>
+        <v>131033362</v>
       </c>
       <c r="B97" t="n">
-        <v>79246</v>
+        <v>78914</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10964,21 +10964,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10988,10 +10988,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>395436</v>
+        <v>395883</v>
       </c>
       <c r="R97" t="n">
-        <v>6804436</v>
+        <v>6804433</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11018,22 +11018,22 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11060,10 +11060,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>131046887</v>
+        <v>131033332</v>
       </c>
       <c r="B98" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11095,10 +11095,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>395449</v>
+        <v>395641</v>
       </c>
       <c r="R98" t="n">
-        <v>6804334</v>
+        <v>6804509</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11125,22 +11125,22 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11167,10 +11167,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>131046780</v>
+        <v>131046895</v>
       </c>
       <c r="B99" t="n">
-        <v>57884</v>
+        <v>79248</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11178,39 +11178,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>395470</v>
+        <v>395436</v>
       </c>
       <c r="R99" t="n">
-        <v>6804530</v>
+        <v>6804436</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11242,7 +11237,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11252,12 +11247,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>11:42</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11284,10 +11274,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>131047019</v>
+        <v>131046780</v>
       </c>
       <c r="B100" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11315,7 +11305,7 @@
       <c r="I100" t="inlineStr"/>
       <c r="M100" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
@@ -11324,10 +11314,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>395446</v>
+        <v>395470</v>
       </c>
       <c r="R100" t="n">
-        <v>6804531</v>
+        <v>6804530</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11359,7 +11349,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11369,19 +11359,19 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>Troliga spår efter tretåig hackspett (barkfälkning)</t>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
       <c r="AE100" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG100" t="b">
         <v>0</v>
@@ -11401,10 +11391,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>131033332</v>
+        <v>131047019</v>
       </c>
       <c r="B101" t="n">
-        <v>79246</v>
+        <v>57886</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11412,34 +11402,39 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>395641</v>
+        <v>395446</v>
       </c>
       <c r="R101" t="n">
-        <v>6804509</v>
+        <v>6804531</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11466,29 +11461,34 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Troliga spår efter tretåig hackspett (barkfälkning)</t>
         </is>
       </c>
       <c r="AD101" t="b">
         <v>0</v>
       </c>
       <c r="AE101" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG101" t="b">
         <v>0</v>
@@ -11508,10 +11508,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>131046952</v>
+        <v>131033349</v>
       </c>
       <c r="B102" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11543,10 +11543,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>395461</v>
+        <v>395757</v>
       </c>
       <c r="R102" t="n">
-        <v>6804521</v>
+        <v>6804291</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11573,22 +11573,22 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11615,10 +11615,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>131046951</v>
+        <v>131046952</v>
       </c>
       <c r="B103" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11650,10 +11650,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>395463</v>
+        <v>395461</v>
       </c>
       <c r="R103" t="n">
-        <v>6804524</v>
+        <v>6804521</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11722,10 +11722,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>131046876</v>
+        <v>131046951</v>
       </c>
       <c r="B104" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11757,10 +11757,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>395457</v>
+        <v>395463</v>
       </c>
       <c r="R104" t="n">
-        <v>6804453</v>
+        <v>6804524</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11792,7 +11792,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11802,7 +11802,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11829,10 +11829,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>131033349</v>
+        <v>131046876</v>
       </c>
       <c r="B105" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11864,10 +11864,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>395757</v>
+        <v>395457</v>
       </c>
       <c r="R105" t="n">
-        <v>6804291</v>
+        <v>6804453</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11894,22 +11894,22 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11936,10 +11936,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>131046796</v>
+        <v>131046890</v>
       </c>
       <c r="B106" t="n">
-        <v>79004</v>
+        <v>79248</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11947,21 +11947,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11971,10 +11971,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>395443</v>
+        <v>395440</v>
       </c>
       <c r="R106" t="n">
-        <v>6804347</v>
+        <v>6804390</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12006,7 +12006,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12016,7 +12016,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12043,10 +12043,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>131046890</v>
+        <v>131047017</v>
       </c>
       <c r="B107" t="n">
-        <v>79246</v>
+        <v>57886</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12054,34 +12054,39 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>395440</v>
+        <v>395448</v>
       </c>
       <c r="R107" t="n">
-        <v>6804390</v>
+        <v>6804508</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12113,7 +12118,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12123,14 +12128,19 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Troliga spår efter tretåig hackspett (barkfälkning)</t>
         </is>
       </c>
       <c r="AD107" t="b">
         <v>0</v>
       </c>
       <c r="AE107" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG107" t="b">
         <v>0</v>
@@ -12150,10 +12160,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>131047017</v>
+        <v>131046796</v>
       </c>
       <c r="B108" t="n">
-        <v>57884</v>
+        <v>79006</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12161,39 +12171,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>395448</v>
+        <v>395443</v>
       </c>
       <c r="R108" t="n">
-        <v>6804508</v>
+        <v>6804347</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12225,7 +12230,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12235,19 +12240,14 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>Troliga spår efter tretåig hackspett (barkfälkning)</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD108" t="b">
         <v>0</v>
       </c>
       <c r="AE108" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG108" t="b">
         <v>0</v>
@@ -12270,7 +12270,7 @@
         <v>131046903</v>
       </c>
       <c r="B109" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12377,7 +12377,7 @@
         <v>131046957</v>
       </c>
       <c r="B110" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12484,7 +12484,7 @@
         <v>131033341</v>
       </c>
       <c r="B111" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>

--- a/artfynd/A 28856-2025 artfynd.xlsx
+++ b/artfynd/A 28856-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131046803</v>
+        <v>131046875</v>
       </c>
       <c r="B2" t="n">
-        <v>79005</v>
+        <v>79249</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>395450</v>
+        <v>395444</v>
       </c>
       <c r="R2" t="n">
-        <v>6804390</v>
+        <v>6804461</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131046747</v>
+        <v>131046947</v>
       </c>
       <c r="B3" t="n">
-        <v>57883</v>
+        <v>79249</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,39 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>395480</v>
+        <v>395461</v>
       </c>
       <c r="R3" t="n">
-        <v>6804496</v>
+        <v>6804551</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131046790</v>
+        <v>131046896</v>
       </c>
       <c r="B4" t="n">
-        <v>57886</v>
+        <v>79249</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,39 +900,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>395416</v>
+        <v>395423</v>
       </c>
       <c r="R4" t="n">
-        <v>6804491</v>
+        <v>6804458</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,12 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:27</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131046875</v>
+        <v>131046872</v>
       </c>
       <c r="B5" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1046,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>395444</v>
+        <v>395434</v>
       </c>
       <c r="R5" t="n">
-        <v>6804461</v>
+        <v>6804484</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1091,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1118,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131046947</v>
+        <v>131046873</v>
       </c>
       <c r="B6" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1153,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>395461</v>
+        <v>395430</v>
       </c>
       <c r="R6" t="n">
-        <v>6804551</v>
+        <v>6804474</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1188,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1198,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1225,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131046896</v>
+        <v>131046995</v>
       </c>
       <c r="B7" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>395423</v>
+        <v>395491</v>
       </c>
       <c r="R7" t="n">
-        <v>6804458</v>
+        <v>6804522</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1295,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1305,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1332,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131046872</v>
+        <v>131046803</v>
       </c>
       <c r="B8" t="n">
-        <v>79248</v>
+        <v>79006</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1343,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1367,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>395434</v>
+        <v>395450</v>
       </c>
       <c r="R8" t="n">
-        <v>6804484</v>
+        <v>6804390</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1402,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1412,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1439,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131046873</v>
+        <v>131046790</v>
       </c>
       <c r="B9" t="n">
-        <v>79248</v>
+        <v>57887</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1450,34 +1435,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>395430</v>
+        <v>395416</v>
       </c>
       <c r="R9" t="n">
-        <v>6804474</v>
+        <v>6804491</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1509,7 +1499,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1519,7 +1509,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1546,10 +1541,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131046995</v>
+        <v>131046747</v>
       </c>
       <c r="B10" t="n">
-        <v>79248</v>
+        <v>57884</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1557,34 +1552,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>395491</v>
+        <v>395480</v>
       </c>
       <c r="R10" t="n">
-        <v>6804522</v>
+        <v>6804496</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1616,7 +1616,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1653,10 +1653,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131046749</v>
+        <v>131033342</v>
       </c>
       <c r="B11" t="n">
-        <v>57883</v>
+        <v>79249</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1664,39 +1664,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>395449</v>
+        <v>395753</v>
       </c>
       <c r="R11" t="n">
-        <v>6804395</v>
+        <v>6804557</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1723,22 +1718,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1765,32 +1760,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131046884</v>
+        <v>131046807</v>
       </c>
       <c r="B12" t="n">
-        <v>79248</v>
+        <v>83212</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1800,10 +1795,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>395489</v>
+        <v>395510</v>
       </c>
       <c r="R12" t="n">
-        <v>6804292</v>
+        <v>6804530</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1835,7 +1830,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1845,7 +1840,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1872,10 +1867,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131046858</v>
+        <v>131046884</v>
       </c>
       <c r="B13" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,10 +1902,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>395570</v>
+        <v>395489</v>
       </c>
       <c r="R13" t="n">
-        <v>6804341</v>
+        <v>6804292</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1942,7 +1937,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1952,7 +1947,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1979,10 +1974,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131033342</v>
+        <v>131046858</v>
       </c>
       <c r="B14" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2014,10 +2009,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>395753</v>
+        <v>395570</v>
       </c>
       <c r="R14" t="n">
-        <v>6804557</v>
+        <v>6804341</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2044,22 +2039,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2086,45 +2081,50 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131046807</v>
+        <v>131046749</v>
       </c>
       <c r="B15" t="n">
-        <v>83211</v>
+        <v>57884</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6439</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>395510</v>
+        <v>395449</v>
       </c>
       <c r="R15" t="n">
-        <v>6804530</v>
+        <v>6804395</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2193,10 +2193,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131033331</v>
+        <v>131046901</v>
       </c>
       <c r="B16" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2228,10 +2228,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>395707</v>
+        <v>395395</v>
       </c>
       <c r="R16" t="n">
-        <v>6804307</v>
+        <v>6804547</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2258,22 +2258,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2300,10 +2300,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131046955</v>
+        <v>131046878</v>
       </c>
       <c r="B17" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>395432</v>
+        <v>395478</v>
       </c>
       <c r="R17" t="n">
-        <v>6804533</v>
+        <v>6804426</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2370,7 +2370,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2407,10 +2407,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131046901</v>
+        <v>131046868</v>
       </c>
       <c r="B18" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2442,10 +2442,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>395395</v>
+        <v>395462</v>
       </c>
       <c r="R18" t="n">
-        <v>6804547</v>
+        <v>6804496</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2477,7 +2477,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2514,10 +2514,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131046878</v>
+        <v>131033348</v>
       </c>
       <c r="B19" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2549,10 +2549,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>395478</v>
+        <v>395756</v>
       </c>
       <c r="R19" t="n">
-        <v>6804426</v>
+        <v>6804343</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2579,22 +2579,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2621,10 +2621,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131046868</v>
+        <v>131046777</v>
       </c>
       <c r="B20" t="n">
-        <v>79248</v>
+        <v>57887</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2632,34 +2632,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>395462</v>
+        <v>395435</v>
       </c>
       <c r="R20" t="n">
-        <v>6804496</v>
+        <v>6804481</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2691,7 +2696,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2701,7 +2706,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2728,10 +2738,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131033348</v>
+        <v>131047009</v>
       </c>
       <c r="B21" t="n">
-        <v>79248</v>
+        <v>57887</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2739,34 +2749,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>395756</v>
+        <v>395494</v>
       </c>
       <c r="R21" t="n">
-        <v>6804343</v>
+        <v>6804551</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2793,22 +2811,27 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Nästan helt avbarkad klen gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2835,10 +2858,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131033283</v>
+        <v>131033331</v>
       </c>
       <c r="B22" t="n">
-        <v>79280</v>
+        <v>79249</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2846,21 +2869,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2870,10 +2893,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>395745</v>
+        <v>395707</v>
       </c>
       <c r="R22" t="n">
-        <v>6804404</v>
+        <v>6804307</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2905,7 +2928,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2915,7 +2938,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2942,10 +2965,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131046777</v>
+        <v>131046955</v>
       </c>
       <c r="B23" t="n">
-        <v>57886</v>
+        <v>79249</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2953,39 +2976,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>395435</v>
+        <v>395432</v>
       </c>
       <c r="R23" t="n">
-        <v>6804481</v>
+        <v>6804533</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3017,7 +3035,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3027,12 +3045,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:46</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3059,10 +3072,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131047009</v>
+        <v>131033283</v>
       </c>
       <c r="B24" t="n">
-        <v>57886</v>
+        <v>79281</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3070,42 +3083,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>395494</v>
+        <v>395745</v>
       </c>
       <c r="R24" t="n">
-        <v>6804551</v>
+        <v>6804404</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3132,27 +3137,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:26</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Nästan helt avbarkad klen gran</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3179,10 +3179,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131033294</v>
+        <v>131033324</v>
       </c>
       <c r="B25" t="n">
-        <v>57886</v>
+        <v>79249</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3190,39 +3190,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>395714</v>
+        <v>395676</v>
       </c>
       <c r="R25" t="n">
-        <v>6804552</v>
+        <v>6804490</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3254,7 +3249,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3264,12 +3259,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:06</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3296,10 +3286,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131033302</v>
+        <v>131046894</v>
       </c>
       <c r="B26" t="n">
-        <v>79006</v>
+        <v>79249</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3307,21 +3297,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3331,10 +3321,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>395679</v>
+        <v>395429</v>
       </c>
       <c r="R26" t="n">
-        <v>6804524</v>
+        <v>6804421</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3361,22 +3351,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3403,10 +3393,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131033324</v>
+        <v>131033344</v>
       </c>
       <c r="B27" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3438,10 +3428,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>395676</v>
+        <v>395753</v>
       </c>
       <c r="R27" t="n">
-        <v>6804490</v>
+        <v>6804482</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3473,7 +3463,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3483,7 +3473,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3510,10 +3500,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131046894</v>
+        <v>131033294</v>
       </c>
       <c r="B28" t="n">
-        <v>79248</v>
+        <v>57887</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3521,34 +3511,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>395429</v>
+        <v>395714</v>
       </c>
       <c r="R28" t="n">
-        <v>6804421</v>
+        <v>6804552</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3575,22 +3570,27 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3617,10 +3617,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131033344</v>
+        <v>131033302</v>
       </c>
       <c r="B29" t="n">
-        <v>79248</v>
+        <v>79007</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3628,21 +3628,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3652,10 +3652,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>395753</v>
+        <v>395679</v>
       </c>
       <c r="R29" t="n">
-        <v>6804482</v>
+        <v>6804524</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3687,7 +3687,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3697,7 +3697,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3727,7 +3727,7 @@
         <v>131046892</v>
       </c>
       <c r="B30" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3831,10 +3831,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131046998</v>
+        <v>131046898</v>
       </c>
       <c r="B31" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3866,10 +3866,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>395494</v>
+        <v>395393</v>
       </c>
       <c r="R31" t="n">
-        <v>6804551</v>
+        <v>6804503</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3901,7 +3901,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3911,7 +3911,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3938,10 +3938,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131046994</v>
+        <v>131046998</v>
       </c>
       <c r="B32" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3973,10 +3973,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>395484</v>
+        <v>395494</v>
       </c>
       <c r="R32" t="n">
-        <v>6804534</v>
+        <v>6804551</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4008,7 +4008,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4018,7 +4018,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4045,50 +4045,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131047035</v>
+        <v>131046994</v>
       </c>
       <c r="B33" t="n">
-        <v>5177</v>
+        <v>79249</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>395505</v>
+        <v>395484</v>
       </c>
       <c r="R33" t="n">
-        <v>6804295</v>
+        <v>6804534</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4120,7 +4115,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4130,7 +4125,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4160,7 +4155,7 @@
         <v>131046885</v>
       </c>
       <c r="B34" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4267,7 +4262,7 @@
         <v>131046956</v>
       </c>
       <c r="B35" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4371,45 +4366,50 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131046898</v>
+        <v>131047035</v>
       </c>
       <c r="B36" t="n">
-        <v>79248</v>
+        <v>5177</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>395393</v>
+        <v>395505</v>
       </c>
       <c r="R36" t="n">
-        <v>6804503</v>
+        <v>6804295</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4481,7 +4481,7 @@
         <v>131046855</v>
       </c>
       <c r="B37" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4588,7 +4588,7 @@
         <v>131046897</v>
       </c>
       <c r="B38" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4695,7 +4695,7 @@
         <v>131033347</v>
       </c>
       <c r="B39" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4799,10 +4799,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131046748</v>
+        <v>131046881</v>
       </c>
       <c r="B40" t="n">
-        <v>57883</v>
+        <v>79249</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4810,39 +4810,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>395453</v>
+        <v>395494</v>
       </c>
       <c r="R40" t="n">
-        <v>6804322</v>
+        <v>6804395</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4874,7 +4869,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4884,7 +4879,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4911,10 +4906,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131046881</v>
+        <v>131046999</v>
       </c>
       <c r="B41" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4946,10 +4941,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>395494</v>
+        <v>395485</v>
       </c>
       <c r="R41" t="n">
-        <v>6804395</v>
+        <v>6804561</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4981,7 +4976,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4991,7 +4986,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5018,10 +5013,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131046999</v>
+        <v>131046859</v>
       </c>
       <c r="B42" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5053,10 +5048,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>395485</v>
+        <v>395566</v>
       </c>
       <c r="R42" t="n">
-        <v>6804561</v>
+        <v>6804349</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5088,7 +5083,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5098,7 +5093,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5125,10 +5120,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131046859</v>
+        <v>131033334</v>
       </c>
       <c r="B43" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5160,10 +5155,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>395566</v>
+        <v>395718</v>
       </c>
       <c r="R43" t="n">
-        <v>6804349</v>
+        <v>6804558</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5190,22 +5185,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5232,10 +5227,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131046805</v>
+        <v>131033346</v>
       </c>
       <c r="B44" t="n">
-        <v>79005</v>
+        <v>79249</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5243,21 +5238,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5267,10 +5262,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>395461</v>
+        <v>395744</v>
       </c>
       <c r="R44" t="n">
-        <v>6804539</v>
+        <v>6804417</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5297,22 +5292,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5339,10 +5334,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131033334</v>
+        <v>131046805</v>
       </c>
       <c r="B45" t="n">
-        <v>79248</v>
+        <v>79006</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5350,21 +5345,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5374,10 +5369,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>395718</v>
+        <v>395461</v>
       </c>
       <c r="R45" t="n">
-        <v>6804558</v>
+        <v>6804539</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5404,22 +5399,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5446,10 +5441,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131033346</v>
+        <v>131046748</v>
       </c>
       <c r="B46" t="n">
-        <v>79248</v>
+        <v>57884</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5457,34 +5452,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>395744</v>
+        <v>395453</v>
       </c>
       <c r="R46" t="n">
-        <v>6804417</v>
+        <v>6804322</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5511,22 +5511,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5556,7 +5556,7 @@
         <v>131033288</v>
       </c>
       <c r="B47" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5670,10 +5670,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131046948</v>
+        <v>131033323</v>
       </c>
       <c r="B48" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5705,10 +5705,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>395462</v>
+        <v>395680</v>
       </c>
       <c r="R48" t="n">
-        <v>6804542</v>
+        <v>6804541</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5735,22 +5735,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5777,10 +5777,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131046712</v>
+        <v>131046949</v>
       </c>
       <c r="B49" t="n">
-        <v>83228</v>
+        <v>79249</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5788,21 +5788,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5812,10 +5812,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>395468</v>
+        <v>395463</v>
       </c>
       <c r="R49" t="n">
-        <v>6804494</v>
+        <v>6804534</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5847,7 +5847,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5857,7 +5857,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5884,10 +5884,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131046949</v>
+        <v>131046948</v>
       </c>
       <c r="B50" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5919,10 +5919,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>395463</v>
+        <v>395462</v>
       </c>
       <c r="R50" t="n">
-        <v>6804534</v>
+        <v>6804542</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5954,7 +5954,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5964,7 +5964,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5994,7 +5994,7 @@
         <v>131046869</v>
       </c>
       <c r="B51" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6098,10 +6098,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131046954</v>
+        <v>131046997</v>
       </c>
       <c r="B52" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6133,10 +6133,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>395446</v>
+        <v>395518</v>
       </c>
       <c r="R52" t="n">
-        <v>6804531</v>
+        <v>6804527</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6168,7 +6168,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6178,7 +6178,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6205,10 +6205,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131046997</v>
+        <v>131046861</v>
       </c>
       <c r="B53" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6240,10 +6240,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>395518</v>
+        <v>395564</v>
       </c>
       <c r="R53" t="n">
-        <v>6804527</v>
+        <v>6804373</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6275,7 +6275,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6285,7 +6285,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6312,10 +6312,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131046861</v>
+        <v>131046712</v>
       </c>
       <c r="B54" t="n">
-        <v>79248</v>
+        <v>83229</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6323,21 +6323,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6347,10 +6347,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>395564</v>
+        <v>395468</v>
       </c>
       <c r="R54" t="n">
-        <v>6804373</v>
+        <v>6804494</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6382,7 +6382,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6392,7 +6392,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6419,10 +6419,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131033323</v>
+        <v>131033352</v>
       </c>
       <c r="B55" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6454,10 +6454,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>395680</v>
+        <v>395857</v>
       </c>
       <c r="R55" t="n">
-        <v>6804541</v>
+        <v>6804292</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6489,7 +6489,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6499,7 +6499,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6526,10 +6526,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131033352</v>
+        <v>131046866</v>
       </c>
       <c r="B56" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6561,10 +6561,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>395857</v>
+        <v>395542</v>
       </c>
       <c r="R56" t="n">
-        <v>6804292</v>
+        <v>6804432</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6591,22 +6591,22 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6633,10 +6633,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131046866</v>
+        <v>131046880</v>
       </c>
       <c r="B57" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6668,10 +6668,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>395542</v>
+        <v>395491</v>
       </c>
       <c r="R57" t="n">
-        <v>6804432</v>
+        <v>6804393</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6703,7 +6703,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6713,7 +6713,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6740,10 +6740,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131046880</v>
+        <v>131046954</v>
       </c>
       <c r="B58" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6775,10 +6775,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>395491</v>
+        <v>395446</v>
       </c>
       <c r="R58" t="n">
-        <v>6804393</v>
+        <v>6804531</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6810,7 +6810,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6820,7 +6820,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6850,7 +6850,7 @@
         <v>131046874</v>
       </c>
       <c r="B59" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6957,7 +6957,7 @@
         <v>131046879</v>
       </c>
       <c r="B60" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7064,7 +7064,7 @@
         <v>131046713</v>
       </c>
       <c r="B61" t="n">
-        <v>83228</v>
+        <v>83229</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7171,7 +7171,7 @@
         <v>131046888</v>
       </c>
       <c r="B62" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7275,10 +7275,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131033321</v>
+        <v>131046882</v>
       </c>
       <c r="B63" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7310,10 +7310,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>395718</v>
+        <v>395493</v>
       </c>
       <c r="R63" t="n">
-        <v>6804573</v>
+        <v>6804376</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7340,22 +7340,22 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7382,10 +7382,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131046882</v>
+        <v>131033327</v>
       </c>
       <c r="B64" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7417,10 +7417,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>395493</v>
+        <v>395671</v>
       </c>
       <c r="R64" t="n">
-        <v>6804376</v>
+        <v>6804435</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7447,22 +7447,22 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7489,10 +7489,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131033327</v>
+        <v>131033326</v>
       </c>
       <c r="B65" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7524,10 +7524,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>395671</v>
+        <v>395665</v>
       </c>
       <c r="R65" t="n">
-        <v>6804435</v>
+        <v>6804439</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7569,7 +7569,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7596,10 +7596,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131033326</v>
+        <v>131046996</v>
       </c>
       <c r="B66" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7631,10 +7631,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>395665</v>
+        <v>395485</v>
       </c>
       <c r="R66" t="n">
-        <v>6804439</v>
+        <v>6804506</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7661,22 +7661,22 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7703,10 +7703,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131046996</v>
+        <v>131046789</v>
       </c>
       <c r="B67" t="n">
-        <v>79248</v>
+        <v>57887</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7714,34 +7714,39 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>395485</v>
+        <v>395495</v>
       </c>
       <c r="R67" t="n">
-        <v>6804506</v>
+        <v>6804385</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7773,7 +7778,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7783,7 +7788,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>09:59</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7810,10 +7820,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131046789</v>
+        <v>131033321</v>
       </c>
       <c r="B68" t="n">
-        <v>57886</v>
+        <v>79249</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7821,39 +7831,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>395495</v>
+        <v>395718</v>
       </c>
       <c r="R68" t="n">
-        <v>6804385</v>
+        <v>6804573</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7880,27 +7885,22 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>09:59</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7927,45 +7927,50 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131033299</v>
+        <v>131033295</v>
       </c>
       <c r="B69" t="n">
-        <v>79272</v>
+        <v>57887</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6434</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>395890</v>
+        <v>395744</v>
       </c>
       <c r="R69" t="n">
-        <v>6804464</v>
+        <v>6804575</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7997,7 +8002,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8007,7 +8012,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8034,32 +8044,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131046993</v>
+        <v>131033299</v>
       </c>
       <c r="B70" t="n">
-        <v>79248</v>
+        <v>79273</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8069,10 +8079,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>395472</v>
+        <v>395890</v>
       </c>
       <c r="R70" t="n">
-        <v>6804550</v>
+        <v>6804464</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8099,22 +8109,22 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8141,10 +8151,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131033353</v>
+        <v>131046993</v>
       </c>
       <c r="B71" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8176,10 +8186,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>395859</v>
+        <v>395472</v>
       </c>
       <c r="R71" t="n">
-        <v>6804312</v>
+        <v>6804550</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8206,22 +8216,22 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8248,10 +8258,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131046856</v>
+        <v>131033353</v>
       </c>
       <c r="B72" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8283,10 +8293,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>395564</v>
+        <v>395859</v>
       </c>
       <c r="R72" t="n">
-        <v>6804311</v>
+        <v>6804312</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8313,22 +8323,22 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8355,10 +8365,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131046877</v>
+        <v>131046856</v>
       </c>
       <c r="B73" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8390,10 +8400,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>395464</v>
+        <v>395564</v>
       </c>
       <c r="R73" t="n">
-        <v>6804442</v>
+        <v>6804311</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8425,7 +8435,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8435,7 +8445,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8462,10 +8472,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131033295</v>
+        <v>131046877</v>
       </c>
       <c r="B74" t="n">
-        <v>57886</v>
+        <v>79249</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8473,39 +8483,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>395744</v>
+        <v>395464</v>
       </c>
       <c r="R74" t="n">
-        <v>6804575</v>
+        <v>6804442</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8532,27 +8537,22 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>13:09</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8582,7 +8582,7 @@
         <v>131033303</v>
       </c>
       <c r="B75" t="n">
-        <v>79006</v>
+        <v>79007</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8689,7 +8689,7 @@
         <v>131046886</v>
       </c>
       <c r="B76" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8796,7 +8796,7 @@
         <v>131046862</v>
       </c>
       <c r="B77" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8903,7 +8903,7 @@
         <v>131046865</v>
       </c>
       <c r="B78" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
         <v>131046854</v>
       </c>
       <c r="B79" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9117,7 +9117,7 @@
         <v>131033330</v>
       </c>
       <c r="B80" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9224,7 +9224,7 @@
         <v>131033322</v>
       </c>
       <c r="B81" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9331,7 +9331,7 @@
         <v>131046883</v>
       </c>
       <c r="B82" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9438,7 +9438,7 @@
         <v>131046889</v>
       </c>
       <c r="B83" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9545,7 +9545,7 @@
         <v>131046857</v>
       </c>
       <c r="B84" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9652,7 +9652,7 @@
         <v>131046893</v>
       </c>
       <c r="B85" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9759,7 +9759,7 @@
         <v>131033333</v>
       </c>
       <c r="B86" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9866,7 +9866,7 @@
         <v>131046860</v>
       </c>
       <c r="B87" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9973,7 +9973,7 @@
         <v>131046902</v>
       </c>
       <c r="B88" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10080,7 +10080,7 @@
         <v>131047018</v>
       </c>
       <c r="B89" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10197,7 +10197,7 @@
         <v>131033293</v>
       </c>
       <c r="B90" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10314,7 +10314,7 @@
         <v>131046870</v>
       </c>
       <c r="B91" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10421,7 +10421,7 @@
         <v>131046891</v>
       </c>
       <c r="B92" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10528,7 +10528,7 @@
         <v>131046950</v>
       </c>
       <c r="B93" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10635,7 +10635,7 @@
         <v>131046992</v>
       </c>
       <c r="B94" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10742,7 +10742,7 @@
         <v>131033345</v>
       </c>
       <c r="B95" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10846,10 +10846,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>131046887</v>
+        <v>131046780</v>
       </c>
       <c r="B96" t="n">
-        <v>79248</v>
+        <v>57887</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10857,34 +10857,39 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>395449</v>
+        <v>395470</v>
       </c>
       <c r="R96" t="n">
-        <v>6804334</v>
+        <v>6804530</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10916,7 +10921,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10926,7 +10931,12 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10953,10 +10963,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>131033362</v>
+        <v>131047019</v>
       </c>
       <c r="B97" t="n">
-        <v>78914</v>
+        <v>57887</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10964,34 +10974,39 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>395883</v>
+        <v>395446</v>
       </c>
       <c r="R97" t="n">
-        <v>6804433</v>
+        <v>6804531</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11018,29 +11033,34 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Troliga spår efter tretåig hackspett (barkfälkning)</t>
         </is>
       </c>
       <c r="AD97" t="b">
         <v>0</v>
       </c>
       <c r="AE97" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG97" t="b">
         <v>0</v>
@@ -11063,7 +11083,7 @@
         <v>131033332</v>
       </c>
       <c r="B98" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11167,10 +11187,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>131046895</v>
+        <v>131046887</v>
       </c>
       <c r="B99" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11202,10 +11222,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>395436</v>
+        <v>395449</v>
       </c>
       <c r="R99" t="n">
-        <v>6804436</v>
+        <v>6804334</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11237,7 +11257,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11247,7 +11267,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11274,10 +11294,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>131046780</v>
+        <v>131046895</v>
       </c>
       <c r="B100" t="n">
-        <v>57886</v>
+        <v>79249</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11285,39 +11305,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>395470</v>
+        <v>395436</v>
       </c>
       <c r="R100" t="n">
-        <v>6804530</v>
+        <v>6804436</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11349,7 +11364,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11359,12 +11374,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>11:42</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11391,10 +11401,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>131047019</v>
+        <v>131033362</v>
       </c>
       <c r="B101" t="n">
-        <v>57886</v>
+        <v>78915</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11402,39 +11412,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>395446</v>
+        <v>395883</v>
       </c>
       <c r="R101" t="n">
-        <v>6804531</v>
+        <v>6804433</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11461,34 +11466,29 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>11:44</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>Troliga spår efter tretåig hackspett (barkfälkning)</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD101" t="b">
         <v>0</v>
       </c>
       <c r="AE101" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG101" t="b">
         <v>0</v>
@@ -11508,10 +11508,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>131033349</v>
+        <v>131046890</v>
       </c>
       <c r="B102" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11543,10 +11543,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>395757</v>
+        <v>395440</v>
       </c>
       <c r="R102" t="n">
-        <v>6804291</v>
+        <v>6804390</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11573,22 +11573,22 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11615,10 +11615,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>131046952</v>
+        <v>131033349</v>
       </c>
       <c r="B103" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11650,10 +11650,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>395461</v>
+        <v>395757</v>
       </c>
       <c r="R103" t="n">
-        <v>6804521</v>
+        <v>6804291</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11680,22 +11680,22 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11722,10 +11722,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>131046951</v>
+        <v>131046952</v>
       </c>
       <c r="B104" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11757,10 +11757,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>395463</v>
+        <v>395461</v>
       </c>
       <c r="R104" t="n">
-        <v>6804524</v>
+        <v>6804521</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11829,10 +11829,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>131046876</v>
+        <v>131046951</v>
       </c>
       <c r="B105" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11864,10 +11864,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>395457</v>
+        <v>395463</v>
       </c>
       <c r="R105" t="n">
-        <v>6804453</v>
+        <v>6804524</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11899,7 +11899,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11909,7 +11909,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11936,10 +11936,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>131046890</v>
+        <v>131046876</v>
       </c>
       <c r="B106" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11971,10 +11971,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>395440</v>
+        <v>395457</v>
       </c>
       <c r="R106" t="n">
-        <v>6804390</v>
+        <v>6804453</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12006,7 +12006,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12016,7 +12016,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12046,7 +12046,7 @@
         <v>131047017</v>
       </c>
       <c r="B107" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12163,7 +12163,7 @@
         <v>131046796</v>
       </c>
       <c r="B108" t="n">
-        <v>79006</v>
+        <v>79007</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12270,7 +12270,7 @@
         <v>131046903</v>
       </c>
       <c r="B109" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12377,7 +12377,7 @@
         <v>131046957</v>
       </c>
       <c r="B110" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12484,7 +12484,7 @@
         <v>131033341</v>
       </c>
       <c r="B111" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>

--- a/artfynd/A 28856-2025 artfynd.xlsx
+++ b/artfynd/A 28856-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131046875</v>
+        <v>131046747</v>
       </c>
       <c r="B2" t="n">
-        <v>79249</v>
+        <v>57884</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>395444</v>
+        <v>395480</v>
       </c>
       <c r="R2" t="n">
-        <v>6804461</v>
+        <v>6804496</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131046947</v>
+        <v>131046875</v>
       </c>
       <c r="B3" t="n">
         <v>79249</v>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>395461</v>
+        <v>395444</v>
       </c>
       <c r="R3" t="n">
-        <v>6804551</v>
+        <v>6804461</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +894,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131046896</v>
+        <v>131046947</v>
       </c>
       <c r="B4" t="n">
         <v>79249</v>
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>395423</v>
+        <v>395461</v>
       </c>
       <c r="R4" t="n">
-        <v>6804458</v>
+        <v>6804551</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +1001,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131046872</v>
+        <v>131046896</v>
       </c>
       <c r="B5" t="n">
         <v>79249</v>
@@ -1031,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>395434</v>
+        <v>395423</v>
       </c>
       <c r="R5" t="n">
-        <v>6804484</v>
+        <v>6804458</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1081,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1108,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131046873</v>
+        <v>131046872</v>
       </c>
       <c r="B6" t="n">
         <v>79249</v>
@@ -1138,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>395430</v>
+        <v>395434</v>
       </c>
       <c r="R6" t="n">
-        <v>6804474</v>
+        <v>6804484</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,7 +1215,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131046995</v>
+        <v>131046873</v>
       </c>
       <c r="B7" t="n">
         <v>79249</v>
@@ -1245,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>395491</v>
+        <v>395430</v>
       </c>
       <c r="R7" t="n">
-        <v>6804522</v>
+        <v>6804474</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1285,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1295,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,10 +1322,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131046803</v>
+        <v>131046995</v>
       </c>
       <c r="B8" t="n">
-        <v>79006</v>
+        <v>79249</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,21 +1333,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>395450</v>
+        <v>395491</v>
       </c>
       <c r="R8" t="n">
-        <v>6804390</v>
+        <v>6804522</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,7 +1392,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1402,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,10 +1429,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131046790</v>
+        <v>131046803</v>
       </c>
       <c r="B9" t="n">
-        <v>57887</v>
+        <v>79006</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1435,39 +1440,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>395416</v>
+        <v>395450</v>
       </c>
       <c r="R9" t="n">
-        <v>6804491</v>
+        <v>6804390</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1509,12 +1509,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:27</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1541,10 +1536,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131046747</v>
+        <v>131046790</v>
       </c>
       <c r="B10" t="n">
-        <v>57884</v>
+        <v>57887</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1552,16 +1547,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1572,7 +1567,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1581,10 +1576,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>395480</v>
+        <v>395416</v>
       </c>
       <c r="R10" t="n">
-        <v>6804496</v>
+        <v>6804491</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1616,7 +1611,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1626,7 +1621,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1867,10 +1867,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131046884</v>
+        <v>131046749</v>
       </c>
       <c r="B13" t="n">
-        <v>79249</v>
+        <v>57884</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1878,34 +1878,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>395489</v>
+        <v>395449</v>
       </c>
       <c r="R13" t="n">
-        <v>6804292</v>
+        <v>6804395</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1937,7 +1942,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1947,7 +1952,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1974,7 +1979,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131046858</v>
+        <v>131046884</v>
       </c>
       <c r="B14" t="n">
         <v>79249</v>
@@ -2009,10 +2014,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>395570</v>
+        <v>395489</v>
       </c>
       <c r="R14" t="n">
-        <v>6804341</v>
+        <v>6804292</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2044,7 +2049,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2054,7 +2059,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2081,10 +2086,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131046749</v>
+        <v>131046858</v>
       </c>
       <c r="B15" t="n">
-        <v>57884</v>
+        <v>79249</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2092,39 +2097,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>395449</v>
+        <v>395570</v>
       </c>
       <c r="R15" t="n">
-        <v>6804395</v>
+        <v>6804341</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2193,7 +2193,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131046901</v>
+        <v>131046878</v>
       </c>
       <c r="B16" t="n">
         <v>79249</v>
@@ -2228,10 +2228,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>395395</v>
+        <v>395478</v>
       </c>
       <c r="R16" t="n">
-        <v>6804547</v>
+        <v>6804426</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2300,7 +2300,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131046878</v>
+        <v>131046868</v>
       </c>
       <c r="B17" t="n">
         <v>79249</v>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>395478</v>
+        <v>395462</v>
       </c>
       <c r="R17" t="n">
-        <v>6804426</v>
+        <v>6804496</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2370,7 +2370,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2407,7 +2407,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131046868</v>
+        <v>131033348</v>
       </c>
       <c r="B18" t="n">
         <v>79249</v>
@@ -2442,10 +2442,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>395462</v>
+        <v>395756</v>
       </c>
       <c r="R18" t="n">
-        <v>6804496</v>
+        <v>6804343</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2472,22 +2472,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2514,7 +2514,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131033348</v>
+        <v>131033331</v>
       </c>
       <c r="B19" t="n">
         <v>79249</v>
@@ -2549,10 +2549,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>395756</v>
+        <v>395707</v>
       </c>
       <c r="R19" t="n">
-        <v>6804343</v>
+        <v>6804307</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2584,7 +2584,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2594,7 +2594,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2621,10 +2621,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131046777</v>
+        <v>131046901</v>
       </c>
       <c r="B20" t="n">
-        <v>57887</v>
+        <v>79249</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2632,39 +2632,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>395435</v>
+        <v>395395</v>
       </c>
       <c r="R20" t="n">
-        <v>6804481</v>
+        <v>6804547</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2696,7 +2691,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2706,12 +2701,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:46</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2738,10 +2728,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131047009</v>
+        <v>131046955</v>
       </c>
       <c r="B21" t="n">
-        <v>57887</v>
+        <v>79249</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2749,42 +2739,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>395494</v>
+        <v>395432</v>
       </c>
       <c r="R21" t="n">
-        <v>6804551</v>
+        <v>6804533</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2816,7 +2798,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2826,12 +2808,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:26</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Nästan helt avbarkad klen gran</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2858,10 +2835,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131033331</v>
+        <v>131033283</v>
       </c>
       <c r="B22" t="n">
-        <v>79249</v>
+        <v>79281</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2869,21 +2846,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2893,10 +2870,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>395707</v>
+        <v>395745</v>
       </c>
       <c r="R22" t="n">
-        <v>6804307</v>
+        <v>6804404</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2928,7 +2905,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2938,7 +2915,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2965,10 +2942,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131046955</v>
+        <v>131046777</v>
       </c>
       <c r="B23" t="n">
-        <v>79249</v>
+        <v>57887</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2976,34 +2953,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>395432</v>
+        <v>395435</v>
       </c>
       <c r="R23" t="n">
-        <v>6804533</v>
+        <v>6804481</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3035,7 +3017,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3045,7 +3027,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3072,10 +3059,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131033283</v>
+        <v>131047009</v>
       </c>
       <c r="B24" t="n">
-        <v>79281</v>
+        <v>57887</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3083,34 +3070,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>395745</v>
+        <v>395494</v>
       </c>
       <c r="R24" t="n">
-        <v>6804404</v>
+        <v>6804551</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3137,22 +3132,27 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Nästan helt avbarkad klen gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3179,10 +3179,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131033324</v>
+        <v>131033302</v>
       </c>
       <c r="B25" t="n">
-        <v>79249</v>
+        <v>79007</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3190,21 +3190,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3214,10 +3214,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>395676</v>
+        <v>395679</v>
       </c>
       <c r="R25" t="n">
-        <v>6804490</v>
+        <v>6804524</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3249,7 +3249,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3259,7 +3259,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3286,7 +3286,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131046894</v>
+        <v>131033324</v>
       </c>
       <c r="B26" t="n">
         <v>79249</v>
@@ -3321,10 +3321,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>395429</v>
+        <v>395676</v>
       </c>
       <c r="R26" t="n">
-        <v>6804421</v>
+        <v>6804490</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3351,22 +3351,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3393,7 +3393,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131033344</v>
+        <v>131046894</v>
       </c>
       <c r="B27" t="n">
         <v>79249</v>
@@ -3428,10 +3428,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>395753</v>
+        <v>395429</v>
       </c>
       <c r="R27" t="n">
-        <v>6804482</v>
+        <v>6804421</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3458,22 +3458,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3500,10 +3500,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131033294</v>
+        <v>131033344</v>
       </c>
       <c r="B28" t="n">
-        <v>57887</v>
+        <v>79249</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3511,39 +3511,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>395714</v>
+        <v>395753</v>
       </c>
       <c r="R28" t="n">
-        <v>6804552</v>
+        <v>6804482</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3575,7 +3570,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3585,12 +3580,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:06</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3617,10 +3607,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131033302</v>
+        <v>131033294</v>
       </c>
       <c r="B29" t="n">
-        <v>79007</v>
+        <v>57887</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3628,34 +3618,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>395679</v>
+        <v>395714</v>
       </c>
       <c r="R29" t="n">
-        <v>6804524</v>
+        <v>6804552</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3687,7 +3682,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3697,7 +3692,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3724,45 +3724,50 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131046892</v>
+        <v>131047035</v>
       </c>
       <c r="B30" t="n">
-        <v>79249</v>
+        <v>5177</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>395445</v>
+        <v>395505</v>
       </c>
       <c r="R30" t="n">
-        <v>6804404</v>
+        <v>6804295</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3794,7 +3799,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3804,7 +3809,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3831,7 +3836,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131046898</v>
+        <v>131046994</v>
       </c>
       <c r="B31" t="n">
         <v>79249</v>
@@ -3866,10 +3871,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>395393</v>
+        <v>395484</v>
       </c>
       <c r="R31" t="n">
-        <v>6804503</v>
+        <v>6804534</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3901,7 +3906,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3911,7 +3916,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3938,7 +3943,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131046998</v>
+        <v>131046885</v>
       </c>
       <c r="B32" t="n">
         <v>79249</v>
@@ -3973,10 +3978,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>395494</v>
+        <v>395486</v>
       </c>
       <c r="R32" t="n">
-        <v>6804551</v>
+        <v>6804289</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4008,7 +4013,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4018,7 +4023,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4045,7 +4050,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131046994</v>
+        <v>131046956</v>
       </c>
       <c r="B33" t="n">
         <v>79249</v>
@@ -4080,10 +4085,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>395484</v>
+        <v>395418</v>
       </c>
       <c r="R33" t="n">
-        <v>6804534</v>
+        <v>6804552</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4115,7 +4120,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4125,7 +4130,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4152,7 +4157,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131046885</v>
+        <v>131046892</v>
       </c>
       <c r="B34" t="n">
         <v>79249</v>
@@ -4187,10 +4192,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>395486</v>
+        <v>395445</v>
       </c>
       <c r="R34" t="n">
-        <v>6804289</v>
+        <v>6804404</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4222,7 +4227,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4232,7 +4237,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4259,7 +4264,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131046956</v>
+        <v>131046898</v>
       </c>
       <c r="B35" t="n">
         <v>79249</v>
@@ -4294,10 +4299,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>395418</v>
+        <v>395393</v>
       </c>
       <c r="R35" t="n">
-        <v>6804552</v>
+        <v>6804503</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4329,7 +4334,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4339,7 +4344,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4366,50 +4371,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131047035</v>
+        <v>131046998</v>
       </c>
       <c r="B36" t="n">
-        <v>5177</v>
+        <v>79249</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>395505</v>
+        <v>395494</v>
       </c>
       <c r="R36" t="n">
-        <v>6804295</v>
+        <v>6804551</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4799,7 +4799,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131046881</v>
+        <v>131033334</v>
       </c>
       <c r="B40" t="n">
         <v>79249</v>
@@ -4834,10 +4834,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>395494</v>
+        <v>395718</v>
       </c>
       <c r="R40" t="n">
-        <v>6804395</v>
+        <v>6804558</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4864,22 +4864,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4906,7 +4906,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131046999</v>
+        <v>131033346</v>
       </c>
       <c r="B41" t="n">
         <v>79249</v>
@@ -4941,10 +4941,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>395485</v>
+        <v>395744</v>
       </c>
       <c r="R41" t="n">
-        <v>6804561</v>
+        <v>6804417</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4971,22 +4971,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5013,10 +5013,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131046859</v>
+        <v>131046805</v>
       </c>
       <c r="B42" t="n">
-        <v>79249</v>
+        <v>79006</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5024,21 +5024,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5048,10 +5048,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>395566</v>
+        <v>395461</v>
       </c>
       <c r="R42" t="n">
-        <v>6804349</v>
+        <v>6804539</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5083,7 +5083,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5093,7 +5093,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5120,7 +5120,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131033334</v>
+        <v>131046881</v>
       </c>
       <c r="B43" t="n">
         <v>79249</v>
@@ -5155,10 +5155,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>395718</v>
+        <v>395494</v>
       </c>
       <c r="R43" t="n">
-        <v>6804558</v>
+        <v>6804395</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5185,22 +5185,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5227,7 +5227,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131033346</v>
+        <v>131046999</v>
       </c>
       <c r="B44" t="n">
         <v>79249</v>
@@ -5262,10 +5262,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>395744</v>
+        <v>395485</v>
       </c>
       <c r="R44" t="n">
-        <v>6804417</v>
+        <v>6804561</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5292,22 +5292,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5334,10 +5334,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131046805</v>
+        <v>131046859</v>
       </c>
       <c r="B45" t="n">
-        <v>79006</v>
+        <v>79249</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5345,21 +5345,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5369,10 +5369,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>395461</v>
+        <v>395566</v>
       </c>
       <c r="R45" t="n">
-        <v>6804539</v>
+        <v>6804349</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5404,7 +5404,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5414,7 +5414,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5670,7 +5670,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131033323</v>
+        <v>131046997</v>
       </c>
       <c r="B48" t="n">
         <v>79249</v>
@@ -5705,10 +5705,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>395680</v>
+        <v>395518</v>
       </c>
       <c r="R48" t="n">
-        <v>6804541</v>
+        <v>6804527</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5735,22 +5735,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5777,10 +5777,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131046949</v>
+        <v>131046712</v>
       </c>
       <c r="B49" t="n">
-        <v>79249</v>
+        <v>83229</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5788,21 +5788,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5812,10 +5812,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>395463</v>
+        <v>395468</v>
       </c>
       <c r="R49" t="n">
-        <v>6804534</v>
+        <v>6804494</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5847,7 +5847,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5857,7 +5857,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5884,7 +5884,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131046948</v>
+        <v>131033352</v>
       </c>
       <c r="B50" t="n">
         <v>79249</v>
@@ -5919,10 +5919,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>395462</v>
+        <v>395857</v>
       </c>
       <c r="R50" t="n">
-        <v>6804542</v>
+        <v>6804292</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5949,22 +5949,22 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5991,7 +5991,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131046869</v>
+        <v>131046866</v>
       </c>
       <c r="B51" t="n">
         <v>79249</v>
@@ -6026,10 +6026,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>395456</v>
+        <v>395542</v>
       </c>
       <c r="R51" t="n">
-        <v>6804500</v>
+        <v>6804432</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6061,7 +6061,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6071,7 +6071,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6098,7 +6098,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131046997</v>
+        <v>131046880</v>
       </c>
       <c r="B52" t="n">
         <v>79249</v>
@@ -6133,10 +6133,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>395518</v>
+        <v>395491</v>
       </c>
       <c r="R52" t="n">
-        <v>6804527</v>
+        <v>6804393</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6168,7 +6168,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6178,7 +6178,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6205,7 +6205,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131046861</v>
+        <v>131046954</v>
       </c>
       <c r="B53" t="n">
         <v>79249</v>
@@ -6240,10 +6240,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>395564</v>
+        <v>395446</v>
       </c>
       <c r="R53" t="n">
-        <v>6804373</v>
+        <v>6804531</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6275,7 +6275,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6285,7 +6285,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6312,10 +6312,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131046712</v>
+        <v>131046861</v>
       </c>
       <c r="B54" t="n">
-        <v>83229</v>
+        <v>79249</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6323,21 +6323,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6347,10 +6347,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>395468</v>
+        <v>395564</v>
       </c>
       <c r="R54" t="n">
-        <v>6804494</v>
+        <v>6804373</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6382,7 +6382,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6392,7 +6392,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6419,7 +6419,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131033352</v>
+        <v>131033323</v>
       </c>
       <c r="B55" t="n">
         <v>79249</v>
@@ -6454,10 +6454,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>395857</v>
+        <v>395680</v>
       </c>
       <c r="R55" t="n">
-        <v>6804292</v>
+        <v>6804541</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6489,7 +6489,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6499,7 +6499,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6526,7 +6526,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131046866</v>
+        <v>131046949</v>
       </c>
       <c r="B56" t="n">
         <v>79249</v>
@@ -6561,10 +6561,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>395542</v>
+        <v>395463</v>
       </c>
       <c r="R56" t="n">
-        <v>6804432</v>
+        <v>6804534</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6596,7 +6596,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6606,7 +6606,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6633,7 +6633,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131046880</v>
+        <v>131046948</v>
       </c>
       <c r="B57" t="n">
         <v>79249</v>
@@ -6668,10 +6668,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>395491</v>
+        <v>395462</v>
       </c>
       <c r="R57" t="n">
-        <v>6804393</v>
+        <v>6804542</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6703,7 +6703,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6713,7 +6713,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6740,7 +6740,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131046954</v>
+        <v>131046869</v>
       </c>
       <c r="B58" t="n">
         <v>79249</v>
@@ -6775,10 +6775,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>395446</v>
+        <v>395456</v>
       </c>
       <c r="R58" t="n">
-        <v>6804531</v>
+        <v>6804500</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6810,7 +6810,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6820,7 +6820,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7275,7 +7275,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131046882</v>
+        <v>131033321</v>
       </c>
       <c r="B63" t="n">
         <v>79249</v>
@@ -7310,10 +7310,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>395493</v>
+        <v>395718</v>
       </c>
       <c r="R63" t="n">
-        <v>6804376</v>
+        <v>6804573</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7340,22 +7340,22 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7382,7 +7382,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131033327</v>
+        <v>131046882</v>
       </c>
       <c r="B64" t="n">
         <v>79249</v>
@@ -7417,10 +7417,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>395671</v>
+        <v>395493</v>
       </c>
       <c r="R64" t="n">
-        <v>6804435</v>
+        <v>6804376</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7447,22 +7447,22 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7596,7 +7596,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131046996</v>
+        <v>131033327</v>
       </c>
       <c r="B66" t="n">
         <v>79249</v>
@@ -7631,10 +7631,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>395485</v>
+        <v>395671</v>
       </c>
       <c r="R66" t="n">
-        <v>6804506</v>
+        <v>6804435</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7661,22 +7661,22 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7703,10 +7703,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131046789</v>
+        <v>131046996</v>
       </c>
       <c r="B67" t="n">
-        <v>57887</v>
+        <v>79249</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7714,39 +7714,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>395495</v>
+        <v>395485</v>
       </c>
       <c r="R67" t="n">
-        <v>6804385</v>
+        <v>6804506</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7778,7 +7773,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7788,12 +7783,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>09:59</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7820,10 +7810,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131033321</v>
+        <v>131046789</v>
       </c>
       <c r="B68" t="n">
-        <v>79249</v>
+        <v>57887</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7831,34 +7821,39 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>395718</v>
+        <v>395495</v>
       </c>
       <c r="R68" t="n">
-        <v>6804573</v>
+        <v>6804385</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7885,22 +7880,27 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>09:59</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7927,50 +7927,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131033295</v>
+        <v>131033299</v>
       </c>
       <c r="B69" t="n">
-        <v>57887</v>
+        <v>79273</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>6434</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>395744</v>
+        <v>395890</v>
       </c>
       <c r="R69" t="n">
-        <v>6804575</v>
+        <v>6804464</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8002,7 +7997,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8012,12 +8007,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:09</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8044,32 +8034,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131033299</v>
+        <v>131046993</v>
       </c>
       <c r="B70" t="n">
-        <v>79273</v>
+        <v>79249</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8079,10 +8069,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>395890</v>
+        <v>395472</v>
       </c>
       <c r="R70" t="n">
-        <v>6804464</v>
+        <v>6804550</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8109,22 +8099,22 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8151,7 +8141,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131046993</v>
+        <v>131033353</v>
       </c>
       <c r="B71" t="n">
         <v>79249</v>
@@ -8186,10 +8176,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>395472</v>
+        <v>395859</v>
       </c>
       <c r="R71" t="n">
-        <v>6804550</v>
+        <v>6804312</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8216,22 +8206,22 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8258,7 +8248,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131033353</v>
+        <v>131046856</v>
       </c>
       <c r="B72" t="n">
         <v>79249</v>
@@ -8293,10 +8283,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>395859</v>
+        <v>395564</v>
       </c>
       <c r="R72" t="n">
-        <v>6804312</v>
+        <v>6804311</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8323,22 +8313,22 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8365,7 +8355,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131046856</v>
+        <v>131046877</v>
       </c>
       <c r="B73" t="n">
         <v>79249</v>
@@ -8400,10 +8390,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>395564</v>
+        <v>395464</v>
       </c>
       <c r="R73" t="n">
-        <v>6804311</v>
+        <v>6804442</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8435,7 +8425,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8445,7 +8435,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8472,10 +8462,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131046877</v>
+        <v>131033295</v>
       </c>
       <c r="B74" t="n">
-        <v>79249</v>
+        <v>57887</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8483,34 +8473,39 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>395464</v>
+        <v>395744</v>
       </c>
       <c r="R74" t="n">
-        <v>6804442</v>
+        <v>6804575</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8537,22 +8532,27 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9863,7 +9863,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>131046860</v>
+        <v>131046902</v>
       </c>
       <c r="B87" t="n">
         <v>79249</v>
@@ -9898,10 +9898,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>395578</v>
+        <v>395389</v>
       </c>
       <c r="R87" t="n">
-        <v>6804350</v>
+        <v>6804555</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9933,7 +9933,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9943,7 +9943,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9970,7 +9970,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>131046902</v>
+        <v>131046860</v>
       </c>
       <c r="B88" t="n">
         <v>79249</v>
@@ -10005,10 +10005,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>395389</v>
+        <v>395578</v>
       </c>
       <c r="R88" t="n">
-        <v>6804555</v>
+        <v>6804350</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10040,7 +10040,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10050,7 +10050,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10311,7 +10311,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>131046870</v>
+        <v>131046950</v>
       </c>
       <c r="B91" t="n">
         <v>79249</v>
@@ -10346,10 +10346,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>395450</v>
+        <v>395470</v>
       </c>
       <c r="R91" t="n">
-        <v>6804507</v>
+        <v>6804530</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10391,7 +10391,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10418,7 +10418,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>131046891</v>
+        <v>131046992</v>
       </c>
       <c r="B92" t="n">
         <v>79249</v>
@@ -10453,10 +10453,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>395453</v>
+        <v>395477</v>
       </c>
       <c r="R92" t="n">
-        <v>6804400</v>
+        <v>6804563</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10488,7 +10488,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10498,7 +10498,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10525,7 +10525,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>131046950</v>
+        <v>131033345</v>
       </c>
       <c r="B93" t="n">
         <v>79249</v>
@@ -10560,10 +10560,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>395470</v>
+        <v>395748</v>
       </c>
       <c r="R93" t="n">
-        <v>6804530</v>
+        <v>6804429</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10590,22 +10590,22 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10632,7 +10632,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>131046992</v>
+        <v>131046870</v>
       </c>
       <c r="B94" t="n">
         <v>79249</v>
@@ -10667,10 +10667,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>395477</v>
+        <v>395450</v>
       </c>
       <c r="R94" t="n">
-        <v>6804563</v>
+        <v>6804507</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10702,7 +10702,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10712,7 +10712,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10739,7 +10739,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>131033345</v>
+        <v>131046891</v>
       </c>
       <c r="B95" t="n">
         <v>79249</v>
@@ -10774,10 +10774,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>395748</v>
+        <v>395453</v>
       </c>
       <c r="R95" t="n">
-        <v>6804429</v>
+        <v>6804400</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10804,22 +10804,22 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10846,10 +10846,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>131046780</v>
+        <v>131033362</v>
       </c>
       <c r="B96" t="n">
-        <v>57887</v>
+        <v>78915</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10857,39 +10857,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>395470</v>
+        <v>395883</v>
       </c>
       <c r="R96" t="n">
-        <v>6804530</v>
+        <v>6804433</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10916,27 +10911,22 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>11:42</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10963,10 +10953,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>131047019</v>
+        <v>131046895</v>
       </c>
       <c r="B97" t="n">
-        <v>57887</v>
+        <v>79249</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10974,39 +10964,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>395446</v>
+        <v>395436</v>
       </c>
       <c r="R97" t="n">
-        <v>6804531</v>
+        <v>6804436</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11038,7 +11023,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11048,19 +11033,14 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>11:44</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Troliga spår efter tretåig hackspett (barkfälkning)</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD97" t="b">
         <v>0</v>
       </c>
       <c r="AE97" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG97" t="b">
         <v>0</v>
@@ -11294,10 +11274,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>131046895</v>
+        <v>131046780</v>
       </c>
       <c r="B100" t="n">
-        <v>79249</v>
+        <v>57887</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11305,34 +11285,39 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>395436</v>
+        <v>395470</v>
       </c>
       <c r="R100" t="n">
-        <v>6804436</v>
+        <v>6804530</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11364,7 +11349,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11374,7 +11359,12 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11401,10 +11391,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>131033362</v>
+        <v>131047019</v>
       </c>
       <c r="B101" t="n">
-        <v>78915</v>
+        <v>57887</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11412,34 +11402,39 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>395883</v>
+        <v>395446</v>
       </c>
       <c r="R101" t="n">
-        <v>6804433</v>
+        <v>6804531</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11466,29 +11461,34 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Troliga spår efter tretåig hackspett (barkfälkning)</t>
         </is>
       </c>
       <c r="AD101" t="b">
         <v>0</v>
       </c>
       <c r="AE101" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG101" t="b">
         <v>0</v>
@@ -11508,7 +11508,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>131046890</v>
+        <v>131046951</v>
       </c>
       <c r="B102" t="n">
         <v>79249</v>
@@ -11543,10 +11543,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>395440</v>
+        <v>395463</v>
       </c>
       <c r="R102" t="n">
-        <v>6804390</v>
+        <v>6804524</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11578,7 +11578,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11615,7 +11615,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>131033349</v>
+        <v>131046952</v>
       </c>
       <c r="B103" t="n">
         <v>79249</v>
@@ -11650,10 +11650,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>395757</v>
+        <v>395461</v>
       </c>
       <c r="R103" t="n">
-        <v>6804291</v>
+        <v>6804521</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11680,22 +11680,22 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11722,7 +11722,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>131046952</v>
+        <v>131046876</v>
       </c>
       <c r="B104" t="n">
         <v>79249</v>
@@ -11757,10 +11757,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>395461</v>
+        <v>395457</v>
       </c>
       <c r="R104" t="n">
-        <v>6804521</v>
+        <v>6804453</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11792,7 +11792,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11802,7 +11802,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11829,7 +11829,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>131046951</v>
+        <v>131046890</v>
       </c>
       <c r="B105" t="n">
         <v>79249</v>
@@ -11864,10 +11864,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>395463</v>
+        <v>395440</v>
       </c>
       <c r="R105" t="n">
-        <v>6804524</v>
+        <v>6804390</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11899,7 +11899,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11909,7 +11909,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11936,7 +11936,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>131046876</v>
+        <v>131033349</v>
       </c>
       <c r="B106" t="n">
         <v>79249</v>
@@ -11971,10 +11971,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>395457</v>
+        <v>395757</v>
       </c>
       <c r="R106" t="n">
-        <v>6804453</v>
+        <v>6804291</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12001,22 +12001,22 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12267,7 +12267,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>131046903</v>
+        <v>131033341</v>
       </c>
       <c r="B109" t="n">
         <v>79249</v>
@@ -12302,10 +12302,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>395384</v>
+        <v>395797</v>
       </c>
       <c r="R109" t="n">
-        <v>6804564</v>
+        <v>6804591</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12332,22 +12332,22 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12374,7 +12374,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>131046957</v>
+        <v>131046903</v>
       </c>
       <c r="B110" t="n">
         <v>79249</v>
@@ -12409,10 +12409,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>395414</v>
+        <v>395384</v>
       </c>
       <c r="R110" t="n">
-        <v>6804565</v>
+        <v>6804564</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12444,7 +12444,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12454,7 +12454,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12481,7 +12481,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>131033341</v>
+        <v>131046957</v>
       </c>
       <c r="B111" t="n">
         <v>79249</v>
@@ -12516,10 +12516,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>395797</v>
+        <v>395414</v>
       </c>
       <c r="R111" t="n">
-        <v>6804591</v>
+        <v>6804565</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12546,22 +12546,22 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD111" t="b">
